--- a/Excel/AchievementConfig.xlsx
+++ b/Excel/AchievementConfig.xlsx
@@ -29,10 +29,35 @@
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
+    <author>Administrator</author>
     <author>admin</author>
   </authors>
   <commentList>
     <comment ref="I3" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Administrator:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+1 普通加法
+2 指数乘法
+3 累加递增</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="K3" authorId="1">
       <text>
         <r>
           <rPr>
@@ -64,7 +89,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="57">
   <si>
     <t>#</t>
   </si>
@@ -81,10 +106,16 @@
     <t>Max</t>
   </si>
   <si>
+    <t>ConType</t>
+  </si>
+  <si>
     <t>Condition</t>
   </si>
   <si>
-    <t>RiseCond</t>
+    <t>ConRiseType</t>
+  </si>
+  <si>
+    <t>CondRiseVue</t>
   </si>
   <si>
     <t>RewardType</t>
@@ -120,22 +151,115 @@
     <t>人物达到{0}级</t>
   </si>
   <si>
+    <t>1 人物等级</t>
+  </si>
+  <si>
+    <t>日复一日</t>
+  </si>
+  <si>
+    <t>游戏天数{0}天</t>
+  </si>
+  <si>
+    <t>2游戏天数</t>
+  </si>
+  <si>
+    <t>用爱发电</t>
+  </si>
+  <si>
+    <t>累计看广告数量{0}个</t>
+  </si>
+  <si>
+    <t>3广告数量</t>
+  </si>
+  <si>
     <t>万法精通</t>
   </si>
   <si>
     <t>人物学习{0}个技能</t>
   </si>
   <si>
+    <t>10 技能数量</t>
+  </si>
+  <si>
     <t>技能大师</t>
   </si>
   <si>
     <t>技能总等级达到{0}</t>
   </si>
   <si>
-    <t>战斗吧，比卡丘</t>
+    <t>11 技能总等级</t>
+  </si>
+  <si>
+    <t>驯兽大师</t>
   </si>
   <si>
     <t>累计获取{0}个宠物</t>
+  </si>
+  <si>
+    <t>101 宠物获取数量</t>
+  </si>
+  <si>
+    <t>装备大师</t>
+  </si>
+  <si>
+    <t>累计获取{0}个装备</t>
+  </si>
+  <si>
+    <t>装备精炼</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 精炼总等级{0}</t>
+  </si>
+  <si>
+    <t>装备强化</t>
+  </si>
+  <si>
+    <t>强化总等级{0}</t>
+  </si>
+  <si>
+    <t>巅峰之路</t>
+  </si>
+  <si>
+    <t>主线副本通过{0}关</t>
+  </si>
+  <si>
+    <t>通关副本</t>
+  </si>
+  <si>
+    <t>小怪杀手</t>
+  </si>
+  <si>
+    <t>击杀小怪{0}个</t>
+  </si>
+  <si>
+    <t>精英杀手</t>
+  </si>
+  <si>
+    <t>击杀精英{0}个</t>
+  </si>
+  <si>
+    <t>头目杀手</t>
+  </si>
+  <si>
+    <t>击杀头目{0}个</t>
+  </si>
+  <si>
+    <t>首领杀手</t>
+  </si>
+  <si>
+    <t>击杀首领{0}个</t>
+  </si>
+  <si>
+    <t>BOSS杀手</t>
+  </si>
+  <si>
+    <t>击杀普通BOSS{0}个</t>
+  </si>
+  <si>
+    <t>区域杀手</t>
+  </si>
+  <si>
+    <t>击杀区域BOSS{0}个</t>
   </si>
 </sst>
 </file>
@@ -781,7 +905,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -792,6 +916,7 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1103,27 +1228,32 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C1:N13"/>
+  <dimension ref="C1:P40"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16" customHeight="1"/>
   <cols>
     <col min="1" max="3" width="9" style="2"/>
     <col min="4" max="4" width="11.5454545454545" style="2" customWidth="1"/>
     <col min="5" max="5" width="15.0909090909091" style="2" customWidth="1"/>
-    <col min="6" max="8" width="16.8181818181818" style="2" customWidth="1"/>
-    <col min="9" max="9" width="15.1818181818182" style="2" customWidth="1"/>
-    <col min="10" max="10" width="13.9090909090909" style="2" customWidth="1"/>
-    <col min="11" max="12" width="13.7272727272727" style="2" customWidth="1"/>
-    <col min="13" max="13" width="22.2727272727273" style="2" customWidth="1"/>
-    <col min="14" max="16384" width="9" style="2"/>
+    <col min="6" max="10" width="16.8181818181818" style="2" customWidth="1"/>
+    <col min="11" max="11" width="15.1818181818182" style="2" customWidth="1"/>
+    <col min="12" max="12" width="13.9090909090909" style="2" customWidth="1"/>
+    <col min="13" max="14" width="13.7272727272727" style="2" customWidth="1"/>
+    <col min="15" max="15" width="22.2727272727273" style="2" customWidth="1"/>
+    <col min="16" max="16" width="21" style="2" customWidth="1"/>
+    <col min="17" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" customHeight="1"/>
-    <row r="2" s="1" customFormat="1" customHeight="1" spans="3:14">
-      <c r="N2" s="1" t="s">
+    <row r="1" s="1" customFormat="1" customHeight="1" spans="3:16">
+      <c r="P1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" s="1" customFormat="1" customHeight="1" spans="3:14">
+    <row r="2" s="1" customFormat="1" customHeight="1" spans="3:16">
+      <c r="P2" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" s="1" customFormat="1" customHeight="1" spans="3:16">
       <c r="C3" s="3" t="s">
         <v>1</v>
       </c>
@@ -1157,11 +1287,19 @@
       <c r="M3" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="N3" s="3"/>
-    </row>
-    <row r="4" s="1" customFormat="1" customHeight="1" spans="3:14">
+      <c r="N3" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="O3" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="P3" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" s="1" customFormat="1" customHeight="1" spans="3:16">
       <c r="C4" s="3" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>2</v>
@@ -1193,45 +1331,57 @@
       <c r="M4" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="N4" s="3"/>
-    </row>
-    <row r="5" s="1" customFormat="1" customHeight="1" spans="3:14">
+      <c r="N4" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="O4" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="P4" s="3"/>
+    </row>
+    <row r="5" s="1" customFormat="1" customHeight="1" spans="3:16">
       <c r="C5" s="3" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G5" s="3" t="s">
         <v>15</v>
       </c>
       <c r="H5" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I5" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="I5" s="3" t="s">
-        <v>13</v>
-      </c>
       <c r="J5" s="3" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="K5" s="3" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="L5" s="3" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="N5" s="3"/>
-    </row>
-    <row r="6" customHeight="1" spans="3:14">
+        <v>15</v>
+      </c>
+      <c r="N5" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="O5" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="P5" s="3"/>
+    </row>
+    <row r="6" customHeight="1" spans="3:16">
       <c r="C6" s="2">
         <v>1</v>
       </c>
@@ -1239,13 +1389,13 @@
         <v>101</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F6" s="1">
         <v>10</v>
       </c>
       <c r="G6" s="1">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="H6" s="1">
         <v>10</v>
@@ -1254,123 +1404,741 @@
         <v>1</v>
       </c>
       <c r="J6" s="1">
+        <v>10</v>
+      </c>
+      <c r="K6" s="1">
+        <v>1</v>
+      </c>
+      <c r="L6" s="1">
         <v>27</v>
       </c>
-      <c r="K6" s="1">
-        <v>5</v>
-      </c>
-      <c r="L6" s="1">
-        <v>5</v>
-      </c>
-      <c r="M6" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="10" customHeight="1" spans="3:14">
-      <c r="C10" s="2">
+      <c r="M6" s="1">
+        <v>5</v>
+      </c>
+      <c r="N6" s="1">
+        <v>5</v>
+      </c>
+      <c r="O6" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="P6" s="3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="7" customHeight="1" spans="3:16">
+      <c r="C7" s="2">
+        <v>2</v>
+      </c>
+      <c r="D7" s="2">
+        <v>101</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="F7" s="2">
+        <v>30</v>
+      </c>
+      <c r="G7" s="2">
+        <v>2</v>
+      </c>
+      <c r="H7" s="2">
+        <v>1</v>
+      </c>
+      <c r="I7" s="2">
+        <v>1</v>
+      </c>
+      <c r="J7" s="2">
+        <v>3</v>
+      </c>
+      <c r="K7" s="1">
+        <v>1</v>
+      </c>
+      <c r="L7" s="1">
+        <v>27</v>
+      </c>
+      <c r="M7" s="1">
+        <v>5</v>
+      </c>
+      <c r="N7" s="1">
+        <v>5</v>
+      </c>
+      <c r="O7" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="P7" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="8" customHeight="1" spans="3:16">
+      <c r="C8" s="2">
+        <v>3</v>
+      </c>
+      <c r="D8" s="2">
+        <v>101</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="F8" s="2">
+        <v>30</v>
+      </c>
+      <c r="G8" s="2">
+        <v>3</v>
+      </c>
+      <c r="H8" s="2">
+        <v>6</v>
+      </c>
+      <c r="I8" s="2">
+        <v>1</v>
+      </c>
+      <c r="J8" s="2">
+        <v>6</v>
+      </c>
+      <c r="K8" s="2">
+        <v>1</v>
+      </c>
+      <c r="L8" s="2">
+        <v>27</v>
+      </c>
+      <c r="M8" s="2">
+        <v>5</v>
+      </c>
+      <c r="N8" s="2">
+        <v>5</v>
+      </c>
+      <c r="O8" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="P8" s="3" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="9" customHeight="1" spans="3:16">
+      <c r="P9" s="3"/>
+    </row>
+    <row r="10" customHeight="1" spans="3:16">
+      <c r="P10" s="3"/>
+    </row>
+    <row r="11" customHeight="1" spans="3:16">
+      <c r="C11" s="2">
         <v>10001</v>
-      </c>
-      <c r="D10" s="2">
-        <v>102</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="F10" s="2">
-        <v>27</v>
-      </c>
-      <c r="G10" s="2">
-        <v>3</v>
-      </c>
-      <c r="H10" s="2">
-        <v>3</v>
-      </c>
-      <c r="I10" s="2">
-        <v>1</v>
-      </c>
-      <c r="J10" s="2">
-        <v>27</v>
-      </c>
-      <c r="K10" s="2">
-        <v>5</v>
-      </c>
-      <c r="L10" s="2">
-        <v>5</v>
-      </c>
-      <c r="M10" s="1" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="11" customHeight="1" spans="3:14">
-      <c r="C11" s="2">
-        <v>10002</v>
       </c>
       <c r="D11" s="2">
         <v>102</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="F11" s="2">
-        <v>300</v>
+        <v>10</v>
       </c>
       <c r="G11" s="2">
         <v>10</v>
       </c>
       <c r="H11" s="2">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="I11" s="2">
         <v>1</v>
       </c>
       <c r="J11" s="2">
+        <v>3</v>
+      </c>
+      <c r="K11" s="2">
+        <v>1</v>
+      </c>
+      <c r="L11" s="2">
         <v>27</v>
       </c>
-      <c r="K11" s="2">
-        <v>5</v>
-      </c>
-      <c r="L11" s="2">
-        <v>5</v>
-      </c>
-      <c r="M11" s="1" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="13" customHeight="1" spans="3:14">
-      <c r="C13" s="2">
-        <v>20001</v>
-      </c>
-      <c r="D13" s="2">
+      <c r="M11" s="2">
+        <v>5</v>
+      </c>
+      <c r="N11" s="2">
+        <v>5</v>
+      </c>
+      <c r="O11" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="P11" s="3" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="12" customHeight="1" spans="3:16">
+      <c r="C12" s="2">
+        <v>10002</v>
+      </c>
+      <c r="D12" s="2">
+        <v>102</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="F12" s="2">
+        <v>10</v>
+      </c>
+      <c r="G12" s="2">
+        <v>11</v>
+      </c>
+      <c r="H12" s="2">
+        <v>10</v>
+      </c>
+      <c r="I12" s="2">
+        <v>1</v>
+      </c>
+      <c r="J12" s="2">
+        <v>10</v>
+      </c>
+      <c r="K12" s="2">
+        <v>1</v>
+      </c>
+      <c r="L12" s="2">
+        <v>27</v>
+      </c>
+      <c r="M12" s="2">
+        <v>5</v>
+      </c>
+      <c r="N12" s="2">
+        <v>5</v>
+      </c>
+      <c r="O12" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="P12" s="3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="13" customHeight="1" spans="3:16">
+      <c r="P13" s="3"/>
+    </row>
+    <row r="14" customHeight="1" spans="3:16">
+      <c r="C14" s="2">
+        <v>103001</v>
+      </c>
+      <c r="D14" s="2">
         <v>103</v>
       </c>
-      <c r="E13" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="F13" s="2">
-        <v>10</v>
-      </c>
-      <c r="G13" s="2">
-        <v>1</v>
-      </c>
-      <c r="H13" s="2">
+      <c r="E14" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="F14" s="2">
+        <v>10</v>
+      </c>
+      <c r="G14" s="2">
+        <v>101</v>
+      </c>
+      <c r="H14" s="2">
+        <v>1</v>
+      </c>
+      <c r="I14" s="2">
+        <v>1</v>
+      </c>
+      <c r="J14" s="2">
         <v>100</v>
       </c>
-      <c r="I13" s="2">
-        <v>1</v>
-      </c>
-      <c r="J13" s="2">
+      <c r="K14" s="2">
+        <v>1</v>
+      </c>
+      <c r="L14" s="2">
         <v>27</v>
       </c>
-      <c r="K13" s="2">
-        <v>5</v>
-      </c>
-      <c r="M13" s="1" t="s">
-        <v>23</v>
-      </c>
+      <c r="M14" s="2">
+        <v>5</v>
+      </c>
+      <c r="N14" s="2">
+        <v>5</v>
+      </c>
+      <c r="O14" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="P14" s="3" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="15" customHeight="1" spans="3:16">
+      <c r="P15" s="3"/>
+    </row>
+    <row r="16" customHeight="1" spans="3:16">
+      <c r="P16" s="3"/>
+    </row>
+    <row r="17" customHeight="1" spans="3:16">
+      <c r="P17" s="3"/>
+    </row>
+    <row r="18" customHeight="1" spans="3:16">
+      <c r="P18" s="3"/>
+    </row>
+    <row r="19" customHeight="1" spans="3:16">
+      <c r="P19" s="3"/>
+    </row>
+    <row r="20" customHeight="1" spans="3:16">
+      <c r="P20" s="3"/>
+    </row>
+    <row r="21" customHeight="1" spans="3:16">
+      <c r="P21" s="3"/>
+    </row>
+    <row r="22" customHeight="1" spans="3:16">
+      <c r="P22" s="3"/>
+    </row>
+    <row r="23" customHeight="1" spans="3:16">
+      <c r="P23" s="3"/>
+    </row>
+    <row r="24" customHeight="1" spans="3:16">
+      <c r="P24" s="3"/>
+    </row>
+    <row r="25" customHeight="1" spans="3:16">
+      <c r="C25" s="2">
+        <v>201001</v>
+      </c>
+      <c r="D25" s="4">
+        <v>201</v>
+      </c>
+      <c r="E25" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="F25" s="2">
+        <v>10</v>
+      </c>
+      <c r="G25" s="4">
+        <v>201</v>
+      </c>
+      <c r="H25" s="2">
+        <v>100</v>
+      </c>
+      <c r="I25" s="2">
+        <v>3</v>
+      </c>
+      <c r="J25" s="2">
+        <v>0</v>
+      </c>
+      <c r="K25" s="2">
+        <v>1</v>
+      </c>
+      <c r="L25" s="2">
+        <v>27</v>
+      </c>
+      <c r="M25" s="2">
+        <v>5</v>
+      </c>
+      <c r="N25" s="2">
+        <v>5</v>
+      </c>
+      <c r="O25" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="P25" s="3"/>
+    </row>
+    <row r="26" customHeight="1" spans="3:16">
+      <c r="C26" s="2">
+        <v>202001</v>
+      </c>
+      <c r="D26" s="4">
+        <v>202</v>
+      </c>
+      <c r="E26" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="F26" s="2">
+        <v>10</v>
+      </c>
+      <c r="G26" s="4">
+        <v>202</v>
+      </c>
+      <c r="H26" s="2">
+        <v>10</v>
+      </c>
+      <c r="I26" s="2">
+        <v>1</v>
+      </c>
+      <c r="J26" s="2">
+        <v>10</v>
+      </c>
+      <c r="K26" s="2">
+        <v>1</v>
+      </c>
+      <c r="L26" s="2">
+        <v>27</v>
+      </c>
+      <c r="M26" s="2">
+        <v>5</v>
+      </c>
+      <c r="N26" s="2">
+        <v>5</v>
+      </c>
+      <c r="O26" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="P26" s="3"/>
+    </row>
+    <row r="27" customHeight="1" spans="3:16">
+      <c r="C27" s="2">
+        <v>203001</v>
+      </c>
+      <c r="D27" s="4">
+        <v>203</v>
+      </c>
+      <c r="E27" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="F27" s="2">
+        <v>10</v>
+      </c>
+      <c r="G27" s="4">
+        <v>203</v>
+      </c>
+      <c r="H27" s="2">
+        <v>10</v>
+      </c>
+      <c r="I27" s="2">
+        <v>1</v>
+      </c>
+      <c r="J27" s="2">
+        <v>10</v>
+      </c>
+      <c r="K27" s="2">
+        <v>1</v>
+      </c>
+      <c r="L27" s="2">
+        <v>27</v>
+      </c>
+      <c r="M27" s="2">
+        <v>5</v>
+      </c>
+      <c r="N27" s="2">
+        <v>5</v>
+      </c>
+      <c r="O27" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="P27" s="3"/>
+    </row>
+    <row r="28" customHeight="1" spans="3:16">
+      <c r="P28" s="3"/>
+    </row>
+    <row r="29" customHeight="1" spans="3:16">
+      <c r="P29" s="3"/>
+    </row>
+    <row r="30" customHeight="1" spans="3:16">
+      <c r="P30" s="3"/>
+    </row>
+    <row r="31" customHeight="1" spans="3:16">
+      <c r="C31" s="2">
+        <v>30001</v>
+      </c>
+      <c r="D31" s="4">
+        <v>301</v>
+      </c>
+      <c r="E31" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="F31" s="2">
+        <v>10</v>
+      </c>
+      <c r="G31" s="2">
+        <v>301</v>
+      </c>
+      <c r="H31" s="2">
+        <v>1</v>
+      </c>
+      <c r="I31" s="2">
+        <v>1</v>
+      </c>
+      <c r="J31" s="2">
+        <v>1</v>
+      </c>
+      <c r="K31" s="2">
+        <v>1</v>
+      </c>
+      <c r="L31" s="2">
+        <v>27</v>
+      </c>
+      <c r="M31" s="2">
+        <v>5</v>
+      </c>
+      <c r="N31" s="2">
+        <v>5</v>
+      </c>
+      <c r="O31" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="P31" s="4" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="32" customHeight="1" spans="3:16">
+      <c r="C32" s="2">
+        <v>30002</v>
+      </c>
+      <c r="D32" s="4">
+        <v>302</v>
+      </c>
+      <c r="E32" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="F32" s="2">
+        <v>10</v>
+      </c>
+      <c r="G32" s="4">
+        <v>302</v>
+      </c>
+      <c r="H32" s="2">
+        <v>1000</v>
+      </c>
+      <c r="I32" s="2">
+        <v>3</v>
+      </c>
+      <c r="J32" s="2">
+        <v>0</v>
+      </c>
+      <c r="K32" s="2">
+        <v>1</v>
+      </c>
+      <c r="L32" s="2">
+        <v>27</v>
+      </c>
+      <c r="M32" s="2">
+        <v>5</v>
+      </c>
+      <c r="N32" s="2">
+        <v>5</v>
+      </c>
+      <c r="O32" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="P32" s="4" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="33" customHeight="1" spans="3:16">
+      <c r="C33" s="2">
+        <v>30003</v>
+      </c>
+      <c r="D33" s="4">
+        <v>303</v>
+      </c>
+      <c r="E33" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="F33" s="2">
+        <v>10</v>
+      </c>
+      <c r="G33" s="4">
+        <v>303</v>
+      </c>
+      <c r="H33" s="2">
+        <v>200</v>
+      </c>
+      <c r="I33" s="2">
+        <v>3</v>
+      </c>
+      <c r="J33" s="2">
+        <v>0</v>
+      </c>
+      <c r="K33" s="2">
+        <v>1</v>
+      </c>
+      <c r="L33" s="2">
+        <v>27</v>
+      </c>
+      <c r="M33" s="2">
+        <v>5</v>
+      </c>
+      <c r="N33" s="2">
+        <v>5</v>
+      </c>
+      <c r="O33" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="P33" s="4" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="34" customHeight="1" spans="3:16">
+      <c r="C34" s="2">
+        <v>30004</v>
+      </c>
+      <c r="D34" s="4">
+        <v>304</v>
+      </c>
+      <c r="E34" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="F34" s="2">
+        <v>10</v>
+      </c>
+      <c r="G34" s="4">
+        <v>304</v>
+      </c>
+      <c r="H34" s="2">
+        <v>50</v>
+      </c>
+      <c r="I34" s="2">
+        <v>3</v>
+      </c>
+      <c r="J34" s="2">
+        <v>0</v>
+      </c>
+      <c r="K34" s="2">
+        <v>1</v>
+      </c>
+      <c r="L34" s="2">
+        <v>27</v>
+      </c>
+      <c r="M34" s="2">
+        <v>5</v>
+      </c>
+      <c r="N34" s="2">
+        <v>5</v>
+      </c>
+      <c r="O34" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="P34" s="4" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="35" customHeight="1" spans="3:16">
+      <c r="C35" s="2">
+        <v>30005</v>
+      </c>
+      <c r="D35" s="4">
+        <v>305</v>
+      </c>
+      <c r="E35" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="F35" s="2">
+        <v>10</v>
+      </c>
+      <c r="G35" s="4">
+        <v>305</v>
+      </c>
+      <c r="H35" s="2">
+        <v>10</v>
+      </c>
+      <c r="I35" s="2">
+        <v>3</v>
+      </c>
+      <c r="J35" s="2">
+        <v>0</v>
+      </c>
+      <c r="K35" s="2">
+        <v>1</v>
+      </c>
+      <c r="L35" s="2">
+        <v>27</v>
+      </c>
+      <c r="M35" s="2">
+        <v>5</v>
+      </c>
+      <c r="N35" s="2">
+        <v>5</v>
+      </c>
+      <c r="O35" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="P35" s="4" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="36" customHeight="1" spans="3:16">
+      <c r="C36" s="2">
+        <v>30006</v>
+      </c>
+      <c r="D36" s="4">
+        <v>306</v>
+      </c>
+      <c r="E36" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="F36" s="2">
+        <v>10</v>
+      </c>
+      <c r="G36" s="4">
+        <v>306</v>
+      </c>
+      <c r="H36" s="2">
+        <v>5</v>
+      </c>
+      <c r="I36" s="2">
+        <v>3</v>
+      </c>
+      <c r="J36" s="2">
+        <v>0</v>
+      </c>
+      <c r="K36" s="2">
+        <v>1</v>
+      </c>
+      <c r="L36" s="2">
+        <v>27</v>
+      </c>
+      <c r="M36" s="2">
+        <v>5</v>
+      </c>
+      <c r="N36" s="2">
+        <v>5</v>
+      </c>
+      <c r="O36" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="P36" s="4" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="37" customHeight="1" spans="3:16">
+      <c r="C37" s="2">
+        <v>30007</v>
+      </c>
+      <c r="D37" s="4">
+        <v>307</v>
+      </c>
+      <c r="E37" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="F37" s="2">
+        <v>10</v>
+      </c>
+      <c r="G37" s="4">
+        <v>307</v>
+      </c>
+      <c r="H37" s="2">
+        <v>1</v>
+      </c>
+      <c r="I37" s="2">
+        <v>3</v>
+      </c>
+      <c r="J37" s="2">
+        <v>0</v>
+      </c>
+      <c r="K37" s="2">
+        <v>1</v>
+      </c>
+      <c r="L37" s="2">
+        <v>27</v>
+      </c>
+      <c r="M37" s="2">
+        <v>5</v>
+      </c>
+      <c r="N37" s="2">
+        <v>5</v>
+      </c>
+      <c r="O37" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="P37" s="4" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="38" customHeight="1" spans="3:16">
+      <c r="P38" s="3"/>
+    </row>
+    <row r="39" customHeight="1" spans="3:16">
+      <c r="P39" s="3"/>
+    </row>
+    <row r="40" customHeight="1" spans="3:16">
+      <c r="P40" s="3"/>
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:N5" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="G3 I3 J3 K3:P3 G4 I4 J4:P4 G5 H5 I5 J5:O5 P10 H3:H4 P5:P9 P11:P30 P38:P40 C3:F5" errorStyle="warning">
       <formula1>COUNTIF($C:$C,C3)&lt;2</formula1>
     </dataValidation>
   </dataValidations>

--- a/Excel/AchievementConfig.xlsx
+++ b/Excel/AchievementConfig.xlsx
@@ -905,7 +905,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -916,7 +916,6 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1688,16 +1687,16 @@
       <c r="C25" s="2">
         <v>201001</v>
       </c>
-      <c r="D25" s="4">
+      <c r="D25" s="1">
         <v>201</v>
       </c>
-      <c r="E25" s="4" t="s">
+      <c r="E25" s="1" t="s">
         <v>36</v>
       </c>
       <c r="F25" s="2">
         <v>10</v>
       </c>
-      <c r="G25" s="4">
+      <c r="G25" s="1">
         <v>201</v>
       </c>
       <c r="H25" s="2">
@@ -1730,16 +1729,16 @@
       <c r="C26" s="2">
         <v>202001</v>
       </c>
-      <c r="D26" s="4">
+      <c r="D26" s="1">
         <v>202</v>
       </c>
-      <c r="E26" s="4" t="s">
+      <c r="E26" s="1" t="s">
         <v>38</v>
       </c>
       <c r="F26" s="2">
         <v>10</v>
       </c>
-      <c r="G26" s="4">
+      <c r="G26" s="1">
         <v>202</v>
       </c>
       <c r="H26" s="2">
@@ -1772,16 +1771,16 @@
       <c r="C27" s="2">
         <v>203001</v>
       </c>
-      <c r="D27" s="4">
+      <c r="D27" s="1">
         <v>203</v>
       </c>
-      <c r="E27" s="4" t="s">
+      <c r="E27" s="1" t="s">
         <v>40</v>
       </c>
       <c r="F27" s="2">
         <v>10</v>
       </c>
-      <c r="G27" s="4">
+      <c r="G27" s="1">
         <v>203</v>
       </c>
       <c r="H27" s="2">
@@ -1823,7 +1822,7 @@
       <c r="C31" s="2">
         <v>30001</v>
       </c>
-      <c r="D31" s="4">
+      <c r="D31" s="1">
         <v>301</v>
       </c>
       <c r="E31" s="2" t="s">
@@ -1833,7 +1832,7 @@
         <v>10</v>
       </c>
       <c r="G31" s="2">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="H31" s="2">
         <v>1</v>
@@ -1859,7 +1858,7 @@
       <c r="O31" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="P31" s="4" t="s">
+      <c r="P31" s="1" t="s">
         <v>44</v>
       </c>
     </row>
@@ -1867,16 +1866,16 @@
       <c r="C32" s="2">
         <v>30002</v>
       </c>
-      <c r="D32" s="4">
+      <c r="D32" s="1">
         <v>302</v>
       </c>
-      <c r="E32" s="4" t="s">
+      <c r="E32" s="1" t="s">
         <v>45</v>
       </c>
       <c r="F32" s="2">
         <v>10</v>
       </c>
-      <c r="G32" s="4">
+      <c r="G32" s="1">
         <v>302</v>
       </c>
       <c r="H32" s="2">
@@ -1903,7 +1902,7 @@
       <c r="O32" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="P32" s="4" t="s">
+      <c r="P32" s="1" t="s">
         <v>45</v>
       </c>
     </row>
@@ -1911,16 +1910,16 @@
       <c r="C33" s="2">
         <v>30003</v>
       </c>
-      <c r="D33" s="4">
+      <c r="D33" s="1">
         <v>303</v>
       </c>
-      <c r="E33" s="4" t="s">
+      <c r="E33" s="1" t="s">
         <v>47</v>
       </c>
       <c r="F33" s="2">
         <v>10</v>
       </c>
-      <c r="G33" s="4">
+      <c r="G33" s="1">
         <v>303</v>
       </c>
       <c r="H33" s="2">
@@ -1947,7 +1946,7 @@
       <c r="O33" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="P33" s="4" t="s">
+      <c r="P33" s="1" t="s">
         <v>47</v>
       </c>
     </row>
@@ -1955,16 +1954,16 @@
       <c r="C34" s="2">
         <v>30004</v>
       </c>
-      <c r="D34" s="4">
+      <c r="D34" s="1">
         <v>304</v>
       </c>
-      <c r="E34" s="4" t="s">
+      <c r="E34" s="1" t="s">
         <v>49</v>
       </c>
       <c r="F34" s="2">
         <v>10</v>
       </c>
-      <c r="G34" s="4">
+      <c r="G34" s="1">
         <v>304</v>
       </c>
       <c r="H34" s="2">
@@ -1991,7 +1990,7 @@
       <c r="O34" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="P34" s="4" t="s">
+      <c r="P34" s="1" t="s">
         <v>49</v>
       </c>
     </row>
@@ -1999,16 +1998,16 @@
       <c r="C35" s="2">
         <v>30005</v>
       </c>
-      <c r="D35" s="4">
+      <c r="D35" s="1">
         <v>305</v>
       </c>
-      <c r="E35" s="4" t="s">
+      <c r="E35" s="1" t="s">
         <v>51</v>
       </c>
       <c r="F35" s="2">
         <v>10</v>
       </c>
-      <c r="G35" s="4">
+      <c r="G35" s="1">
         <v>305</v>
       </c>
       <c r="H35" s="2">
@@ -2035,7 +2034,7 @@
       <c r="O35" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="P35" s="4" t="s">
+      <c r="P35" s="1" t="s">
         <v>51</v>
       </c>
     </row>
@@ -2043,16 +2042,16 @@
       <c r="C36" s="2">
         <v>30006</v>
       </c>
-      <c r="D36" s="4">
+      <c r="D36" s="1">
         <v>306</v>
       </c>
-      <c r="E36" s="4" t="s">
+      <c r="E36" s="1" t="s">
         <v>53</v>
       </c>
       <c r="F36" s="2">
         <v>10</v>
       </c>
-      <c r="G36" s="4">
+      <c r="G36" s="1">
         <v>306</v>
       </c>
       <c r="H36" s="2">
@@ -2079,7 +2078,7 @@
       <c r="O36" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="P36" s="4" t="s">
+      <c r="P36" s="1" t="s">
         <v>53</v>
       </c>
     </row>
@@ -2087,16 +2086,16 @@
       <c r="C37" s="2">
         <v>30007</v>
       </c>
-      <c r="D37" s="4">
+      <c r="D37" s="1">
         <v>307</v>
       </c>
-      <c r="E37" s="4" t="s">
+      <c r="E37" s="1" t="s">
         <v>55</v>
       </c>
       <c r="F37" s="2">
         <v>10</v>
       </c>
-      <c r="G37" s="4">
+      <c r="G37" s="1">
         <v>307</v>
       </c>
       <c r="H37" s="2">
@@ -2123,7 +2122,7 @@
       <c r="O37" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="P37" s="4" t="s">
+      <c r="P37" s="1" t="s">
         <v>55</v>
       </c>
     </row>
@@ -2138,7 +2137,7 @@
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="G3 I3 J3 K3:P3 G4 I4 J4:P4 G5 H5 I5 J5:O5 P10 H3:H4 P5:P9 P11:P30 P38:P40 C3:F5" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="P6:P30 P38:P40 C3:P5" errorStyle="warning">
       <formula1>COUNTIF($C:$C,C3)&lt;2</formula1>
     </dataValidation>
   </dataValidations>

--- a/Excel/AchievementConfig.xlsx
+++ b/Excel/AchievementConfig.xlsx
@@ -89,7 +89,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="60">
   <si>
     <t>#</t>
   </si>
@@ -121,13 +121,13 @@
     <t>RewardType</t>
   </si>
   <si>
-    <t>AtrId</t>
-  </si>
-  <si>
-    <t>AtrVue</t>
-  </si>
-  <si>
-    <t>AtrVueRise</t>
+    <t>AtrIdList</t>
+  </si>
+  <si>
+    <t>AtrVueList</t>
+  </si>
+  <si>
+    <t>AtrVueRiseList</t>
   </si>
   <si>
     <t>Memo</t>
@@ -145,7 +145,16 @@
     <t>long</t>
   </si>
   <si>
+    <t>int[]</t>
+  </si>
+  <si>
     <t>超越自我</t>
+  </si>
+  <si>
+    <t>3,93</t>
+  </si>
+  <si>
+    <t>10,1</t>
   </si>
   <si>
     <t>人物达到{0}级</t>
@@ -916,6 +925,7 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1367,13 +1377,13 @@
         <v>15</v>
       </c>
       <c r="L5" s="3" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="N5" s="3" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="O5" s="3" t="s">
         <v>16</v>
@@ -1388,7 +1398,7 @@
         <v>101</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F6" s="1">
         <v>10</v>
@@ -1408,20 +1418,20 @@
       <c r="K6" s="1">
         <v>1</v>
       </c>
-      <c r="L6" s="1">
-        <v>27</v>
-      </c>
-      <c r="M6" s="1">
-        <v>5</v>
-      </c>
-      <c r="N6" s="1">
-        <v>5</v>
+      <c r="L6" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="M6" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="N6" s="4" t="s">
+        <v>21</v>
       </c>
       <c r="O6" s="1" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="P6" s="3" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
     </row>
     <row r="7" customHeight="1" spans="3:16">
@@ -1432,7 +1442,7 @@
         <v>101</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="F7" s="2">
         <v>30</v>
@@ -1452,20 +1462,20 @@
       <c r="K7" s="1">
         <v>1</v>
       </c>
-      <c r="L7" s="1">
-        <v>27</v>
-      </c>
-      <c r="M7" s="1">
-        <v>5</v>
-      </c>
-      <c r="N7" s="1">
-        <v>5</v>
+      <c r="L7" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="M7" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="N7" s="4" t="s">
+        <v>21</v>
       </c>
       <c r="O7" s="2" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="P7" s="3" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
     </row>
     <row r="8" customHeight="1" spans="3:16">
@@ -1476,7 +1486,7 @@
         <v>101</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="F8" s="2">
         <v>30</v>
@@ -1496,20 +1506,20 @@
       <c r="K8" s="2">
         <v>1</v>
       </c>
-      <c r="L8" s="2">
-        <v>27</v>
-      </c>
-      <c r="M8" s="2">
-        <v>5</v>
-      </c>
-      <c r="N8" s="2">
-        <v>5</v>
+      <c r="L8" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="M8" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="N8" s="4" t="s">
+        <v>21</v>
       </c>
       <c r="O8" s="2" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="P8" s="3" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
     </row>
     <row r="9" customHeight="1" spans="3:16">
@@ -1526,7 +1536,7 @@
         <v>102</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="F11" s="2">
         <v>10</v>
@@ -1546,20 +1556,20 @@
       <c r="K11" s="2">
         <v>1</v>
       </c>
-      <c r="L11" s="2">
-        <v>27</v>
-      </c>
-      <c r="M11" s="2">
-        <v>5</v>
-      </c>
-      <c r="N11" s="2">
-        <v>5</v>
+      <c r="L11" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="M11" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="N11" s="4" t="s">
+        <v>21</v>
       </c>
       <c r="O11" s="1" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="P11" s="3" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
     </row>
     <row r="12" customHeight="1" spans="3:16">
@@ -1570,7 +1580,7 @@
         <v>102</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="F12" s="2">
         <v>10</v>
@@ -1590,20 +1600,20 @@
       <c r="K12" s="2">
         <v>1</v>
       </c>
-      <c r="L12" s="2">
-        <v>27</v>
-      </c>
-      <c r="M12" s="2">
-        <v>5</v>
-      </c>
-      <c r="N12" s="2">
-        <v>5</v>
+      <c r="L12" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="M12" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="N12" s="4" t="s">
+        <v>21</v>
       </c>
       <c r="O12" s="1" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="P12" s="3" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
     </row>
     <row r="13" customHeight="1" spans="3:16">
@@ -1617,7 +1627,7 @@
         <v>103</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="F14" s="2">
         <v>10</v>
@@ -1637,20 +1647,20 @@
       <c r="K14" s="2">
         <v>1</v>
       </c>
-      <c r="L14" s="2">
-        <v>27</v>
-      </c>
-      <c r="M14" s="2">
-        <v>5</v>
-      </c>
-      <c r="N14" s="2">
-        <v>5</v>
+      <c r="L14" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="M14" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="N14" s="4" t="s">
+        <v>21</v>
       </c>
       <c r="O14" s="1" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="P14" s="3" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
     </row>
     <row r="15" customHeight="1" spans="3:16">
@@ -1691,7 +1701,7 @@
         <v>201</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="F25" s="2">
         <v>10</v>
@@ -1711,17 +1721,17 @@
       <c r="K25" s="2">
         <v>1</v>
       </c>
-      <c r="L25" s="2">
-        <v>27</v>
-      </c>
-      <c r="M25" s="2">
-        <v>5</v>
-      </c>
-      <c r="N25" s="2">
-        <v>5</v>
+      <c r="L25" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="M25" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="N25" s="4" t="s">
+        <v>21</v>
       </c>
       <c r="O25" s="1" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="P25" s="3"/>
     </row>
@@ -1733,7 +1743,7 @@
         <v>202</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="F26" s="2">
         <v>10</v>
@@ -1753,17 +1763,17 @@
       <c r="K26" s="2">
         <v>1</v>
       </c>
-      <c r="L26" s="2">
-        <v>27</v>
-      </c>
-      <c r="M26" s="2">
-        <v>5</v>
-      </c>
-      <c r="N26" s="2">
-        <v>5</v>
+      <c r="L26" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="M26" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="N26" s="4" t="s">
+        <v>21</v>
       </c>
       <c r="O26" s="2" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="P26" s="3"/>
     </row>
@@ -1775,7 +1785,7 @@
         <v>203</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="F27" s="2">
         <v>10</v>
@@ -1795,17 +1805,17 @@
       <c r="K27" s="2">
         <v>1</v>
       </c>
-      <c r="L27" s="2">
-        <v>27</v>
-      </c>
-      <c r="M27" s="2">
-        <v>5</v>
-      </c>
-      <c r="N27" s="2">
-        <v>5</v>
+      <c r="L27" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="M27" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="N27" s="4" t="s">
+        <v>21</v>
       </c>
       <c r="O27" s="2" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="P27" s="3"/>
     </row>
@@ -1826,7 +1836,7 @@
         <v>301</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="F31" s="2">
         <v>10</v>
@@ -1846,20 +1856,20 @@
       <c r="K31" s="2">
         <v>1</v>
       </c>
-      <c r="L31" s="2">
-        <v>27</v>
-      </c>
-      <c r="M31" s="2">
-        <v>5</v>
-      </c>
-      <c r="N31" s="2">
-        <v>5</v>
+      <c r="L31" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="M31" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="N31" s="4" t="s">
+        <v>21</v>
       </c>
       <c r="O31" s="2" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="P31" s="1" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
     </row>
     <row r="32" customHeight="1" spans="3:16">
@@ -1870,7 +1880,7 @@
         <v>302</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="F32" s="2">
         <v>10</v>
@@ -1890,20 +1900,20 @@
       <c r="K32" s="2">
         <v>1</v>
       </c>
-      <c r="L32" s="2">
-        <v>27</v>
-      </c>
-      <c r="M32" s="2">
-        <v>5</v>
-      </c>
-      <c r="N32" s="2">
-        <v>5</v>
+      <c r="L32" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="M32" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="N32" s="4" t="s">
+        <v>21</v>
       </c>
       <c r="O32" s="2" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="P32" s="1" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
     </row>
     <row r="33" customHeight="1" spans="3:16">
@@ -1914,7 +1924,7 @@
         <v>303</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="F33" s="2">
         <v>10</v>
@@ -1934,20 +1944,20 @@
       <c r="K33" s="2">
         <v>1</v>
       </c>
-      <c r="L33" s="2">
-        <v>27</v>
-      </c>
-      <c r="M33" s="2">
-        <v>5</v>
-      </c>
-      <c r="N33" s="2">
-        <v>5</v>
+      <c r="L33" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="M33" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="N33" s="4" t="s">
+        <v>21</v>
       </c>
       <c r="O33" s="2" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="P33" s="1" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
     </row>
     <row r="34" customHeight="1" spans="3:16">
@@ -1958,7 +1968,7 @@
         <v>304</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="F34" s="2">
         <v>10</v>
@@ -1978,20 +1988,20 @@
       <c r="K34" s="2">
         <v>1</v>
       </c>
-      <c r="L34" s="2">
-        <v>27</v>
-      </c>
-      <c r="M34" s="2">
-        <v>5</v>
-      </c>
-      <c r="N34" s="2">
-        <v>5</v>
+      <c r="L34" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="M34" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="N34" s="4" t="s">
+        <v>21</v>
       </c>
       <c r="O34" s="2" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="P34" s="1" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
     </row>
     <row r="35" customHeight="1" spans="3:16">
@@ -2002,7 +2012,7 @@
         <v>305</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="F35" s="2">
         <v>10</v>
@@ -2022,20 +2032,20 @@
       <c r="K35" s="2">
         <v>1</v>
       </c>
-      <c r="L35" s="2">
-        <v>27</v>
-      </c>
-      <c r="M35" s="2">
-        <v>5</v>
-      </c>
-      <c r="N35" s="2">
-        <v>5</v>
+      <c r="L35" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="M35" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="N35" s="4" t="s">
+        <v>21</v>
       </c>
       <c r="O35" s="2" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="P35" s="1" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
     </row>
     <row r="36" customHeight="1" spans="3:16">
@@ -2046,7 +2056,7 @@
         <v>306</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="F36" s="2">
         <v>10</v>
@@ -2066,20 +2076,20 @@
       <c r="K36" s="2">
         <v>1</v>
       </c>
-      <c r="L36" s="2">
-        <v>27</v>
-      </c>
-      <c r="M36" s="2">
-        <v>5</v>
-      </c>
-      <c r="N36" s="2">
-        <v>5</v>
+      <c r="L36" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="M36" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="N36" s="4" t="s">
+        <v>21</v>
       </c>
       <c r="O36" s="2" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="P36" s="1" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
     </row>
     <row r="37" customHeight="1" spans="3:16">
@@ -2090,7 +2100,7 @@
         <v>307</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="F37" s="2">
         <v>10</v>
@@ -2110,20 +2120,20 @@
       <c r="K37" s="2">
         <v>1</v>
       </c>
-      <c r="L37" s="2">
-        <v>27</v>
-      </c>
-      <c r="M37" s="2">
-        <v>5</v>
-      </c>
-      <c r="N37" s="2">
-        <v>5</v>
+      <c r="L37" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="M37" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="N37" s="4" t="s">
+        <v>21</v>
       </c>
       <c r="O37" s="2" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="P37" s="1" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
     </row>
     <row r="38" customHeight="1" spans="3:16">

--- a/Excel/AchievementConfig.xlsx
+++ b/Excel/AchievementConfig.xlsx
@@ -52,8 +52,8 @@
           </rPr>
           <t xml:space="preserve">
 1 普通加法
-2 指数乘法
-3 累加递增</t>
+2 累加递增
+3 指数乘法</t>
         </r>
       </text>
     </comment>
@@ -1889,10 +1889,10 @@
         <v>302</v>
       </c>
       <c r="H32" s="2">
-        <v>1000</v>
+        <v>100000</v>
       </c>
       <c r="I32" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J32" s="2">
         <v>0</v>
@@ -1933,10 +1933,10 @@
         <v>303</v>
       </c>
       <c r="H33" s="2">
-        <v>200</v>
+        <v>10000</v>
       </c>
       <c r="I33" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J33" s="2">
         <v>0</v>
@@ -1977,10 +1977,10 @@
         <v>304</v>
       </c>
       <c r="H34" s="2">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="I34" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J34" s="2">
         <v>0</v>
@@ -2021,10 +2021,10 @@
         <v>305</v>
       </c>
       <c r="H35" s="2">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="I35" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J35" s="2">
         <v>0</v>
@@ -2065,10 +2065,10 @@
         <v>306</v>
       </c>
       <c r="H36" s="2">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="I36" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J36" s="2">
         <v>0</v>
@@ -2112,7 +2112,7 @@
         <v>1</v>
       </c>
       <c r="I37" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J37" s="2">
         <v>0</v>

--- a/Excel/AchievementConfig.xlsx
+++ b/Excel/AchievementConfig.xlsx
@@ -89,7 +89,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="72">
   <si>
     <t>#</t>
   </si>
@@ -127,7 +127,7 @@
     <t>AtrVueList</t>
   </si>
   <si>
-    <t>AtrVueRiseList</t>
+    <t>AtrRiseTypeList</t>
   </si>
   <si>
     <t>Memo</t>
@@ -151,66 +151,87 @@
     <t>超越自我</t>
   </si>
   <si>
+    <t>1003,93</t>
+  </si>
+  <si>
+    <t>1,1</t>
+  </si>
+  <si>
+    <t>人物达到{0}级</t>
+  </si>
+  <si>
+    <t>1 人物等级</t>
+  </si>
+  <si>
+    <t>日复一日</t>
+  </si>
+  <si>
+    <t>1001,93</t>
+  </si>
+  <si>
+    <t>游戏天数{0}天</t>
+  </si>
+  <si>
+    <t>2游戏天数</t>
+  </si>
+  <si>
+    <t>用爱发电</t>
+  </si>
+  <si>
     <t>3,93</t>
   </si>
   <si>
+    <t>50,1</t>
+  </si>
+  <si>
+    <t>2,1</t>
+  </si>
+  <si>
+    <t>累计看广告数量{0}个</t>
+  </si>
+  <si>
+    <t>3广告数量</t>
+  </si>
+  <si>
+    <t>万法精通</t>
+  </si>
+  <si>
+    <t>10,93</t>
+  </si>
+  <si>
+    <t>人物学习{0}个技能</t>
+  </si>
+  <si>
+    <t>10 技能数量</t>
+  </si>
+  <si>
+    <t>技能大师</t>
+  </si>
+  <si>
+    <t>11,93</t>
+  </si>
+  <si>
+    <t>技能总等级达到{0}</t>
+  </si>
+  <si>
+    <t>11 技能总等级</t>
+  </si>
+  <si>
+    <t>驯兽大师</t>
+  </si>
+  <si>
+    <t>累计获取{0}个宠物</t>
+  </si>
+  <si>
+    <t>101 宠物获取数量</t>
+  </si>
+  <si>
+    <t>装备大师</t>
+  </si>
+  <si>
     <t>10,1</t>
   </si>
   <si>
-    <t>人物达到{0}级</t>
-  </si>
-  <si>
-    <t>1 人物等级</t>
-  </si>
-  <si>
-    <t>日复一日</t>
-  </si>
-  <si>
-    <t>游戏天数{0}天</t>
-  </si>
-  <si>
-    <t>2游戏天数</t>
-  </si>
-  <si>
-    <t>用爱发电</t>
-  </si>
-  <si>
-    <t>累计看广告数量{0}个</t>
-  </si>
-  <si>
-    <t>3广告数量</t>
-  </si>
-  <si>
-    <t>万法精通</t>
-  </si>
-  <si>
-    <t>人物学习{0}个技能</t>
-  </si>
-  <si>
-    <t>10 技能数量</t>
-  </si>
-  <si>
-    <t>技能大师</t>
-  </si>
-  <si>
-    <t>技能总等级达到{0}</t>
-  </si>
-  <si>
-    <t>11 技能总等级</t>
-  </si>
-  <si>
-    <t>驯兽大师</t>
-  </si>
-  <si>
-    <t>累计获取{0}个宠物</t>
-  </si>
-  <si>
-    <t>101 宠物获取数量</t>
-  </si>
-  <si>
-    <t>装备大师</t>
-  </si>
-  <si>
     <t>累计获取{0}个装备</t>
   </si>
   <si>
@@ -229,6 +250,9 @@
     <t>巅峰之路</t>
   </si>
   <si>
+    <t>2003,93</t>
+  </si>
+  <si>
     <t>主线副本通过{0}关</t>
   </si>
   <si>
@@ -238,12 +262,21 @@
     <t>小怪杀手</t>
   </si>
   <si>
+    <t>1,93</t>
+  </si>
+  <si>
+    <t>500,1</t>
+  </si>
+  <si>
     <t>击杀小怪{0}个</t>
   </si>
   <si>
     <t>精英杀手</t>
   </si>
   <si>
+    <t>2,93</t>
+  </si>
+  <si>
     <t>击杀精英{0}个</t>
   </si>
   <si>
@@ -266,6 +299,9 @@
   </si>
   <si>
     <t>区域杀手</t>
+  </si>
+  <si>
+    <t>10003,93</t>
   </si>
   <si>
     <t>击杀区域BOSS{0}个</t>
@@ -1246,7 +1282,8 @@
     <col min="6" max="10" width="16.8181818181818" style="2" customWidth="1"/>
     <col min="11" max="11" width="15.1818181818182" style="2" customWidth="1"/>
     <col min="12" max="12" width="13.9090909090909" style="2" customWidth="1"/>
-    <col min="13" max="14" width="13.7272727272727" style="2" customWidth="1"/>
+    <col min="13" max="13" width="13.7272727272727" style="2" customWidth="1"/>
+    <col min="14" max="14" width="16.6363636363636" style="2" customWidth="1"/>
     <col min="15" max="15" width="22.2727272727273" style="2" customWidth="1"/>
     <col min="16" max="16" width="21" style="2" customWidth="1"/>
     <col min="17" max="16384" width="9" style="2"/>
@@ -1463,7 +1500,7 @@
         <v>1</v>
       </c>
       <c r="L7" s="4" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="M7" s="4" t="s">
         <v>21</v>
@@ -1472,10 +1509,10 @@
         <v>21</v>
       </c>
       <c r="O7" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="P7" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="8" customHeight="1" spans="3:16">
@@ -1486,7 +1523,7 @@
         <v>101</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F8" s="2">
         <v>30</v>
@@ -1507,19 +1544,19 @@
         <v>1</v>
       </c>
       <c r="L8" s="4" t="s">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="M8" s="4" t="s">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="N8" s="4" t="s">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="O8" s="2" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="P8" s="3" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
     </row>
     <row r="9" customHeight="1" spans="3:16">
@@ -1536,7 +1573,7 @@
         <v>102</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F11" s="2">
         <v>10</v>
@@ -1557,7 +1594,7 @@
         <v>1</v>
       </c>
       <c r="L11" s="4" t="s">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="M11" s="4" t="s">
         <v>21</v>
@@ -1566,10 +1603,10 @@
         <v>21</v>
       </c>
       <c r="O11" s="1" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="P11" s="3" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
     </row>
     <row r="12" customHeight="1" spans="3:16">
@@ -1580,7 +1617,7 @@
         <v>102</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="F12" s="2">
         <v>10</v>
@@ -1601,7 +1638,7 @@
         <v>1</v>
       </c>
       <c r="L12" s="4" t="s">
-        <v>20</v>
+        <v>39</v>
       </c>
       <c r="M12" s="4" t="s">
         <v>21</v>
@@ -1610,10 +1647,10 @@
         <v>21</v>
       </c>
       <c r="O12" s="1" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="P12" s="3" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
     </row>
     <row r="13" customHeight="1" spans="3:16">
@@ -1627,7 +1664,7 @@
         <v>103</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="F14" s="2">
         <v>10</v>
@@ -1639,7 +1676,7 @@
         <v>1</v>
       </c>
       <c r="I14" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J14" s="2">
         <v>100</v>
@@ -1648,19 +1685,19 @@
         <v>1</v>
       </c>
       <c r="L14" s="4" t="s">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="M14" s="4" t="s">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="N14" s="4" t="s">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="O14" s="1" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="P14" s="3" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
     </row>
     <row r="15" customHeight="1" spans="3:16">
@@ -1701,7 +1738,7 @@
         <v>201</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="F25" s="2">
         <v>10</v>
@@ -1722,16 +1759,16 @@
         <v>1</v>
       </c>
       <c r="L25" s="4" t="s">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="M25" s="4" t="s">
-        <v>21</v>
+        <v>46</v>
       </c>
       <c r="N25" s="4" t="s">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="O25" s="1" t="s">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="P25" s="3"/>
     </row>
@@ -1743,7 +1780,7 @@
         <v>202</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="F26" s="2">
         <v>10</v>
@@ -1773,7 +1810,7 @@
         <v>21</v>
       </c>
       <c r="O26" s="2" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="P26" s="3"/>
     </row>
@@ -1785,7 +1822,7 @@
         <v>203</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="F27" s="2">
         <v>10</v>
@@ -1815,7 +1852,7 @@
         <v>21</v>
       </c>
       <c r="O27" s="2" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="P27" s="3"/>
     </row>
@@ -1836,7 +1873,7 @@
         <v>301</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="F31" s="2">
         <v>10</v>
@@ -1857,7 +1894,7 @@
         <v>1</v>
       </c>
       <c r="L31" s="4" t="s">
-        <v>20</v>
+        <v>53</v>
       </c>
       <c r="M31" s="4" t="s">
         <v>21</v>
@@ -1866,10 +1903,10 @@
         <v>21</v>
       </c>
       <c r="O31" s="2" t="s">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="P31" s="1" t="s">
-        <v>47</v>
+        <v>55</v>
       </c>
     </row>
     <row r="32" customHeight="1" spans="3:16">
@@ -1880,7 +1917,7 @@
         <v>302</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="F32" s="2">
         <v>10</v>
@@ -1901,19 +1938,19 @@
         <v>1</v>
       </c>
       <c r="L32" s="4" t="s">
-        <v>20</v>
+        <v>57</v>
       </c>
       <c r="M32" s="4" t="s">
-        <v>21</v>
+        <v>58</v>
       </c>
       <c r="N32" s="4" t="s">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="O32" s="2" t="s">
-        <v>49</v>
+        <v>59</v>
       </c>
       <c r="P32" s="1" t="s">
-        <v>48</v>
+        <v>56</v>
       </c>
     </row>
     <row r="33" customHeight="1" spans="3:16">
@@ -1924,7 +1961,7 @@
         <v>303</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="F33" s="2">
         <v>10</v>
@@ -1945,19 +1982,19 @@
         <v>1</v>
       </c>
       <c r="L33" s="4" t="s">
-        <v>20</v>
+        <v>61</v>
       </c>
       <c r="M33" s="4" t="s">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="N33" s="4" t="s">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="O33" s="2" t="s">
-        <v>51</v>
+        <v>62</v>
       </c>
       <c r="P33" s="1" t="s">
-        <v>50</v>
+        <v>60</v>
       </c>
     </row>
     <row r="34" customHeight="1" spans="3:16">
@@ -1968,7 +2005,7 @@
         <v>304</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>52</v>
+        <v>63</v>
       </c>
       <c r="F34" s="2">
         <v>10</v>
@@ -1989,19 +2026,19 @@
         <v>1</v>
       </c>
       <c r="L34" s="4" t="s">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="M34" s="4" t="s">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="N34" s="4" t="s">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="O34" s="2" t="s">
-        <v>53</v>
+        <v>64</v>
       </c>
       <c r="P34" s="1" t="s">
-        <v>52</v>
+        <v>63</v>
       </c>
     </row>
     <row r="35" customHeight="1" spans="3:16">
@@ -2012,7 +2049,7 @@
         <v>305</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>54</v>
+        <v>65</v>
       </c>
       <c r="F35" s="2">
         <v>10</v>
@@ -2042,10 +2079,10 @@
         <v>21</v>
       </c>
       <c r="O35" s="2" t="s">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="P35" s="1" t="s">
-        <v>54</v>
+        <v>65</v>
       </c>
     </row>
     <row r="36" customHeight="1" spans="3:16">
@@ -2056,7 +2093,7 @@
         <v>306</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>56</v>
+        <v>67</v>
       </c>
       <c r="F36" s="2">
         <v>10</v>
@@ -2077,7 +2114,7 @@
         <v>1</v>
       </c>
       <c r="L36" s="4" t="s">
-        <v>20</v>
+        <v>53</v>
       </c>
       <c r="M36" s="4" t="s">
         <v>21</v>
@@ -2086,10 +2123,10 @@
         <v>21</v>
       </c>
       <c r="O36" s="2" t="s">
-        <v>57</v>
+        <v>68</v>
       </c>
       <c r="P36" s="1" t="s">
-        <v>56</v>
+        <v>67</v>
       </c>
     </row>
     <row r="37" customHeight="1" spans="3:16">
@@ -2100,7 +2137,7 @@
         <v>307</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>58</v>
+        <v>69</v>
       </c>
       <c r="F37" s="2">
         <v>10</v>
@@ -2121,7 +2158,7 @@
         <v>1</v>
       </c>
       <c r="L37" s="4" t="s">
-        <v>20</v>
+        <v>70</v>
       </c>
       <c r="M37" s="4" t="s">
         <v>21</v>
@@ -2130,10 +2167,10 @@
         <v>21</v>
       </c>
       <c r="O37" s="2" t="s">
-        <v>59</v>
+        <v>71</v>
       </c>
       <c r="P37" s="1" t="s">
-        <v>58</v>
+        <v>69</v>
       </c>
     </row>
     <row r="38" customHeight="1" spans="3:16">

--- a/Excel/AchievementConfig.xlsx
+++ b/Excel/AchievementConfig.xlsx
@@ -89,7 +89,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="75">
   <si>
     <t>#</t>
   </si>
@@ -305,6 +305,15 @@
   </si>
   <si>
     <t>击杀区域BOSS{0}个</t>
+  </si>
+  <si>
+    <t>龙城守护者</t>
+  </si>
+  <si>
+    <t>27,93</t>
+  </si>
+  <si>
+    <t>通关守卫龙城{0}层</t>
   </si>
 </sst>
 </file>
@@ -962,6 +971,9 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" quotePrefix="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1273,7 +1285,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C1:P40"/>
+  <dimension ref="C1:P42"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16" customHeight="1"/>
   <cols>
     <col min="1" max="3" width="9" style="2"/>
@@ -1741,13 +1753,13 @@
         <v>45</v>
       </c>
       <c r="F25" s="2">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="G25" s="1">
         <v>201</v>
       </c>
       <c r="H25" s="2">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="I25" s="2">
         <v>3</v>
@@ -1783,7 +1795,7 @@
         <v>48</v>
       </c>
       <c r="F26" s="2">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="G26" s="1">
         <v>202</v>
@@ -1825,7 +1837,7 @@
         <v>50</v>
       </c>
       <c r="F27" s="2">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="G27" s="1">
         <v>203</v>
@@ -1876,7 +1888,7 @@
         <v>52</v>
       </c>
       <c r="F31" s="2">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="G31" s="2">
         <v>300</v>
@@ -2181,6 +2193,47 @@
     </row>
     <row r="40" customHeight="1" spans="3:16">
       <c r="P40" s="3"/>
+    </row>
+    <row r="42" customHeight="1" spans="3:16">
+      <c r="C42" s="2">
+        <v>40001</v>
+      </c>
+      <c r="D42" s="2">
+        <v>401</v>
+      </c>
+      <c r="E42" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="F42" s="2">
+        <v>10</v>
+      </c>
+      <c r="G42" s="2">
+        <v>8</v>
+      </c>
+      <c r="H42" s="2">
+        <v>10</v>
+      </c>
+      <c r="I42" s="2">
+        <v>1</v>
+      </c>
+      <c r="J42" s="2">
+        <v>10</v>
+      </c>
+      <c r="K42" s="2">
+        <v>1</v>
+      </c>
+      <c r="L42" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="M42" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="N42" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="O42" s="2" t="s">
+        <v>74</v>
+      </c>
     </row>
   </sheetData>
   <dataValidations count="1">

--- a/Excel/AchievementConfig.xlsx
+++ b/Excel/AchievementConfig.xlsx
@@ -89,7 +89,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="77">
   <si>
     <t>#</t>
   </si>
@@ -247,6 +247,15 @@
     <t>强化总等级{0}</t>
   </si>
   <si>
+    <t>传世备强化</t>
+  </si>
+  <si>
+    <t>27,93</t>
+  </si>
+  <si>
+    <t>传世强化总等级{0}</t>
+  </si>
+  <si>
     <t>巅峰之路</t>
   </si>
   <si>
@@ -308,9 +317,6 @@
   </si>
   <si>
     <t>龙城守护者</t>
-  </si>
-  <si>
-    <t>27,93</t>
   </si>
   <si>
     <t>通关守卫龙城{0}层</t>
@@ -1869,6 +1875,45 @@
       <c r="P27" s="3"/>
     </row>
     <row r="28" customHeight="1" spans="3:16">
+      <c r="C28" s="2">
+        <v>203002</v>
+      </c>
+      <c r="D28" s="2">
+        <v>204</v>
+      </c>
+      <c r="E28" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="F28" s="2">
+        <v>10</v>
+      </c>
+      <c r="G28" s="2">
+        <v>204</v>
+      </c>
+      <c r="H28" s="2">
+        <v>24</v>
+      </c>
+      <c r="I28" s="2">
+        <v>1</v>
+      </c>
+      <c r="J28" s="2">
+        <v>24</v>
+      </c>
+      <c r="K28" s="2">
+        <v>1</v>
+      </c>
+      <c r="L28" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="M28" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="N28" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="O28" s="2" t="s">
+        <v>54</v>
+      </c>
       <c r="P28" s="3"/>
     </row>
     <row r="29" customHeight="1" spans="3:16">
@@ -1885,7 +1930,7 @@
         <v>301</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="F31" s="2">
         <v>30</v>
@@ -1906,7 +1951,7 @@
         <v>1</v>
       </c>
       <c r="L31" s="4" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="M31" s="4" t="s">
         <v>21</v>
@@ -1915,10 +1960,10 @@
         <v>21</v>
       </c>
       <c r="O31" s="2" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="P31" s="1" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
     </row>
     <row r="32" customHeight="1" spans="3:16">
@@ -1929,7 +1974,7 @@
         <v>302</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="F32" s="2">
         <v>10</v>
@@ -1950,19 +1995,19 @@
         <v>1</v>
       </c>
       <c r="L32" s="4" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="M32" s="4" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="N32" s="4" t="s">
         <v>31</v>
       </c>
       <c r="O32" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="P32" s="1" t="s">
         <v>59</v>
-      </c>
-      <c r="P32" s="1" t="s">
-        <v>56</v>
       </c>
     </row>
     <row r="33" customHeight="1" spans="3:16">
@@ -1973,7 +2018,7 @@
         <v>303</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="F33" s="2">
         <v>10</v>
@@ -1994,7 +2039,7 @@
         <v>1</v>
       </c>
       <c r="L33" s="4" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="M33" s="4" t="s">
         <v>30</v>
@@ -2003,10 +2048,10 @@
         <v>31</v>
       </c>
       <c r="O33" s="2" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="P33" s="1" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
     </row>
     <row r="34" customHeight="1" spans="3:16">
@@ -2017,7 +2062,7 @@
         <v>304</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="F34" s="2">
         <v>10</v>
@@ -2047,10 +2092,10 @@
         <v>31</v>
       </c>
       <c r="O34" s="2" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="P34" s="1" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
     </row>
     <row r="35" customHeight="1" spans="3:16">
@@ -2061,7 +2106,7 @@
         <v>305</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="F35" s="2">
         <v>10</v>
@@ -2091,10 +2136,10 @@
         <v>21</v>
       </c>
       <c r="O35" s="2" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="P35" s="1" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
     </row>
     <row r="36" customHeight="1" spans="3:16">
@@ -2105,7 +2150,7 @@
         <v>306</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="F36" s="2">
         <v>10</v>
@@ -2126,7 +2171,7 @@
         <v>1</v>
       </c>
       <c r="L36" s="4" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="M36" s="4" t="s">
         <v>21</v>
@@ -2135,10 +2180,10 @@
         <v>21</v>
       </c>
       <c r="O36" s="2" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="P36" s="1" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
     </row>
     <row r="37" customHeight="1" spans="3:16">
@@ -2149,7 +2194,7 @@
         <v>307</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="F37" s="2">
         <v>10</v>
@@ -2170,7 +2215,7 @@
         <v>1</v>
       </c>
       <c r="L37" s="4" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="M37" s="4" t="s">
         <v>21</v>
@@ -2179,10 +2224,10 @@
         <v>21</v>
       </c>
       <c r="O37" s="2" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="P37" s="1" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
     </row>
     <row r="38" customHeight="1" spans="3:16">
@@ -2202,7 +2247,7 @@
         <v>401</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="F42" s="2">
         <v>10</v>
@@ -2223,7 +2268,7 @@
         <v>1</v>
       </c>
       <c r="L42" s="5" t="s">
-        <v>73</v>
+        <v>53</v>
       </c>
       <c r="M42" s="4" t="s">
         <v>21</v>
@@ -2232,7 +2277,7 @@
         <v>21</v>
       </c>
       <c r="O42" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/AchievementConfig.xlsx
+++ b/Excel/AchievementConfig.xlsx
@@ -8,6 +8,7 @@
   </bookViews>
   <sheets>
     <sheet name="属性奖励" sheetId="1" r:id="rId1"/>
+    <sheet name="神秘彩蛋" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -88,8 +89,93 @@
 </comments>
 </file>
 
+<file path=xl/comments2.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>Administrator</author>
+    <author>admin</author>
+  </authors>
+  <commentList>
+    <comment ref="G3" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Administrator:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+10001,击杀小怪概率获得
+10002，击杀区域boss概率获得</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="I3" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Administrator:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+1 普通加法
+2 累加递增
+3 指数乘法</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="K3" authorId="1">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>admin:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+1 增加属性
+2 减少词条上限
+3 回收精炼石增加
+4 魂环碎片掉落增加
+5 减少闯关寻怪时间
+6 技能出战栏</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="253" uniqueCount="112">
   <si>
     <t>#</t>
   </si>
@@ -310,9 +396,6 @@
     <t>区域杀手</t>
   </si>
   <si>
-    <t>10003,93</t>
-  </si>
-  <si>
     <t>击杀区域BOSS{0}个</t>
   </si>
   <si>
@@ -320,6 +403,114 @@
   </si>
   <si>
     <t>通关守卫龙城{0}层</t>
+  </si>
+  <si>
+    <t>保护脆皮</t>
+  </si>
+  <si>
+    <t>1,1001</t>
+  </si>
+  <si>
+    <t>4000,4</t>
+  </si>
+  <si>
+    <t>杀怪概率获取</t>
+  </si>
+  <si>
+    <t>增加血量</t>
+  </si>
+  <si>
+    <t>我要输出</t>
+  </si>
+  <si>
+    <t>2,1002</t>
+  </si>
+  <si>
+    <t>200,2</t>
+  </si>
+  <si>
+    <t>增加攻击</t>
+  </si>
+  <si>
+    <t>我不想死</t>
+  </si>
+  <si>
+    <t>3,1003</t>
+  </si>
+  <si>
+    <t>增加防御</t>
+  </si>
+  <si>
+    <t>给点钱把</t>
+  </si>
+  <si>
+    <t>81,85</t>
+  </si>
+  <si>
+    <t>增加杀敌金币</t>
+  </si>
+  <si>
+    <t>我想升级</t>
+  </si>
+  <si>
+    <t>82,86</t>
+  </si>
+  <si>
+    <t>增加杀敌经验</t>
+  </si>
+  <si>
+    <t>弱点是什么</t>
+  </si>
+  <si>
+    <t>21,93</t>
+  </si>
+  <si>
+    <t>增加暴击</t>
+  </si>
+  <si>
+    <t>你不要动</t>
+  </si>
+  <si>
+    <t>13,93</t>
+  </si>
+  <si>
+    <t>增加命中</t>
+  </si>
+  <si>
+    <t>打不中我</t>
+  </si>
+  <si>
+    <t>14,93</t>
+  </si>
+  <si>
+    <t>增加闪避</t>
+  </si>
+  <si>
+    <t>传奇人生</t>
+  </si>
+  <si>
+    <t>5000,5</t>
+  </si>
+  <si>
+    <t>？？？</t>
+  </si>
+  <si>
+    <t>全身传奇装备</t>
+  </si>
+  <si>
+    <t>百折不挠</t>
+  </si>
+  <si>
+    <t>500,5</t>
+  </si>
+  <si>
+    <t>死亡100次</t>
+  </si>
+  <si>
+    <t>全职大师</t>
+  </si>
+  <si>
+    <t>上阵3系职业的技能</t>
   </si>
 </sst>
 </file>
@@ -1759,7 +1950,7 @@
         <v>45</v>
       </c>
       <c r="F25" s="2">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="G25" s="1">
         <v>201</v>
@@ -1801,7 +1992,7 @@
         <v>48</v>
       </c>
       <c r="F26" s="2">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="G26" s="1">
         <v>202</v>
@@ -1843,7 +2034,7 @@
         <v>50</v>
       </c>
       <c r="F27" s="2">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="G27" s="1">
         <v>203</v>
@@ -2215,7 +2406,7 @@
         <v>1</v>
       </c>
       <c r="L37" s="4" t="s">
-        <v>73</v>
+        <v>56</v>
       </c>
       <c r="M37" s="4" t="s">
         <v>21</v>
@@ -2224,7 +2415,7 @@
         <v>21</v>
       </c>
       <c r="O37" s="2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="P37" s="1" t="s">
         <v>72</v>
@@ -2247,7 +2438,7 @@
         <v>401</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F42" s="2">
         <v>10</v>
@@ -2277,7 +2468,7 @@
         <v>21</v>
       </c>
       <c r="O42" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
   </sheetData>
@@ -2291,4 +2482,657 @@
   <headerFooter/>
   <legacyDrawing r:id="rId2"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="C1:P20"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16" customHeight="1"/>
+  <cols>
+    <col min="1" max="3" width="9" style="2"/>
+    <col min="4" max="4" width="11.5454545454545" style="2" customWidth="1"/>
+    <col min="5" max="5" width="15.0909090909091" style="2" customWidth="1"/>
+    <col min="6" max="10" width="16.8181818181818" style="2" customWidth="1"/>
+    <col min="11" max="11" width="15.1818181818182" style="2" customWidth="1"/>
+    <col min="12" max="12" width="13.9090909090909" style="2" customWidth="1"/>
+    <col min="13" max="13" width="13.7272727272727" style="2" customWidth="1"/>
+    <col min="14" max="14" width="16.6363636363636" style="2" customWidth="1"/>
+    <col min="15" max="15" width="22.2727272727273" style="2" customWidth="1"/>
+    <col min="16" max="16" width="21" style="2" customWidth="1"/>
+    <col min="17" max="16384" width="9" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" s="1" customFormat="1" customHeight="1" spans="3:16">
+      <c r="P1" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" s="1" customFormat="1" customHeight="1" spans="3:16">
+      <c r="P2" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" s="1" customFormat="1" customHeight="1" spans="3:16">
+      <c r="C3" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="I3" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="J3" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K3" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="L3" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="M3" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="N3" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="O3" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="P3" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" s="1" customFormat="1" customHeight="1" spans="3:16">
+      <c r="C4" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="I4" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="J4" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K4" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="L4" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="M4" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="N4" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="O4" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="P4" s="3"/>
+    </row>
+    <row r="5" s="1" customFormat="1" customHeight="1" spans="3:16">
+      <c r="C5" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I5" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J5" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="K5" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="L5" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="M5" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="N5" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="O5" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="P5" s="3"/>
+    </row>
+    <row r="6" s="2" customFormat="1" customHeight="1" spans="3:16">
+      <c r="C6" s="2">
+        <v>50001</v>
+      </c>
+      <c r="D6" s="2">
+        <v>501</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="F6" s="2">
+        <v>10</v>
+      </c>
+      <c r="G6" s="2">
+        <v>10001</v>
+      </c>
+      <c r="H6" s="2">
+        <v>0</v>
+      </c>
+      <c r="I6" s="2">
+        <v>0</v>
+      </c>
+      <c r="J6" s="2">
+        <v>0</v>
+      </c>
+      <c r="K6" s="2">
+        <v>1</v>
+      </c>
+      <c r="L6" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="M6" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="N6" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="O6" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="P6" s="2" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="7" s="2" customFormat="1" customHeight="1" spans="3:16">
+      <c r="C7" s="2">
+        <v>50002</v>
+      </c>
+      <c r="D7" s="2">
+        <v>501</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="F7" s="2">
+        <v>10</v>
+      </c>
+      <c r="G7" s="2">
+        <v>10001</v>
+      </c>
+      <c r="H7" s="2">
+        <v>0</v>
+      </c>
+      <c r="I7" s="2">
+        <v>0</v>
+      </c>
+      <c r="J7" s="2">
+        <v>0</v>
+      </c>
+      <c r="K7" s="2">
+        <v>1</v>
+      </c>
+      <c r="L7" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="M7" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="N7" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="O7" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="P7" s="2" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="8" s="2" customFormat="1" customHeight="1" spans="3:16">
+      <c r="C8" s="2">
+        <v>50003</v>
+      </c>
+      <c r="D8" s="2">
+        <v>501</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="F8" s="2">
+        <v>10</v>
+      </c>
+      <c r="G8" s="2">
+        <v>10001</v>
+      </c>
+      <c r="H8" s="2">
+        <v>0</v>
+      </c>
+      <c r="I8" s="2">
+        <v>0</v>
+      </c>
+      <c r="J8" s="2">
+        <v>0</v>
+      </c>
+      <c r="K8" s="2">
+        <v>1</v>
+      </c>
+      <c r="L8" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="M8" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="N8" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="O8" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="P8" s="2" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="9" s="2" customFormat="1" customHeight="1" spans="3:16">
+      <c r="C9" s="2">
+        <v>50004</v>
+      </c>
+      <c r="D9" s="2">
+        <v>501</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="F9" s="2">
+        <v>10</v>
+      </c>
+      <c r="G9" s="2">
+        <v>10001</v>
+      </c>
+      <c r="H9" s="2">
+        <v>0</v>
+      </c>
+      <c r="I9" s="2">
+        <v>0</v>
+      </c>
+      <c r="J9" s="2">
+        <v>0</v>
+      </c>
+      <c r="K9" s="2">
+        <v>1</v>
+      </c>
+      <c r="L9" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="M9" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="N9" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="O9" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="P9" s="2" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="10" s="2" customFormat="1" customHeight="1" spans="3:16">
+      <c r="C10" s="2">
+        <v>50005</v>
+      </c>
+      <c r="D10" s="2">
+        <v>501</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="F10" s="2">
+        <v>10</v>
+      </c>
+      <c r="G10" s="2">
+        <v>10001</v>
+      </c>
+      <c r="H10" s="2">
+        <v>0</v>
+      </c>
+      <c r="I10" s="2">
+        <v>0</v>
+      </c>
+      <c r="J10" s="2">
+        <v>0</v>
+      </c>
+      <c r="K10" s="2">
+        <v>1</v>
+      </c>
+      <c r="L10" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="M10" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="N10" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="O10" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="P10" s="2" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="11" s="2" customFormat="1" customHeight="1" spans="3:16">
+      <c r="C11" s="2">
+        <v>50006</v>
+      </c>
+      <c r="D11" s="2">
+        <v>501</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="F11" s="2">
+        <v>10</v>
+      </c>
+      <c r="G11" s="2">
+        <v>10002</v>
+      </c>
+      <c r="H11" s="2">
+        <v>0</v>
+      </c>
+      <c r="I11" s="2">
+        <v>0</v>
+      </c>
+      <c r="J11" s="2">
+        <v>0</v>
+      </c>
+      <c r="K11" s="2">
+        <v>1</v>
+      </c>
+      <c r="L11" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="M11" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="N11" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="O11" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="P11" s="2" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="12" s="2" customFormat="1" customHeight="1" spans="3:16">
+      <c r="C12" s="2">
+        <v>50007</v>
+      </c>
+      <c r="D12" s="2">
+        <v>501</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="F12" s="2">
+        <v>10</v>
+      </c>
+      <c r="G12" s="2">
+        <v>10002</v>
+      </c>
+      <c r="H12" s="2">
+        <v>0</v>
+      </c>
+      <c r="I12" s="2">
+        <v>0</v>
+      </c>
+      <c r="J12" s="2">
+        <v>0</v>
+      </c>
+      <c r="K12" s="2">
+        <v>1</v>
+      </c>
+      <c r="L12" s="5" t="s">
+        <v>98</v>
+      </c>
+      <c r="M12" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="N12" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="O12" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="P12" s="2" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="13" s="2" customFormat="1" customHeight="1" spans="3:16">
+      <c r="C13" s="2">
+        <v>50008</v>
+      </c>
+      <c r="D13" s="2">
+        <v>501</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="F13" s="2">
+        <v>10</v>
+      </c>
+      <c r="G13" s="2">
+        <v>10002</v>
+      </c>
+      <c r="H13" s="2">
+        <v>0</v>
+      </c>
+      <c r="I13" s="2">
+        <v>0</v>
+      </c>
+      <c r="J13" s="2">
+        <v>0</v>
+      </c>
+      <c r="K13" s="2">
+        <v>1</v>
+      </c>
+      <c r="L13" s="5" t="s">
+        <v>101</v>
+      </c>
+      <c r="M13" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="N13" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="O13" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="P13" s="2" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="18" s="2" customFormat="1" customHeight="1" spans="3:16">
+      <c r="C18" s="2">
+        <v>52001</v>
+      </c>
+      <c r="D18" s="2">
+        <v>502</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="F18" s="2">
+        <v>1</v>
+      </c>
+      <c r="G18" s="2">
+        <v>0</v>
+      </c>
+      <c r="H18" s="2">
+        <v>0</v>
+      </c>
+      <c r="I18" s="2">
+        <v>0</v>
+      </c>
+      <c r="J18" s="2">
+        <v>0</v>
+      </c>
+      <c r="K18" s="2">
+        <v>1</v>
+      </c>
+      <c r="L18" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="M18" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="N18" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="O18" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="P18" s="2" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="19" customHeight="1" spans="3:16">
+      <c r="C19" s="2">
+        <v>52002</v>
+      </c>
+      <c r="D19" s="2">
+        <v>502</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="F19" s="2">
+        <v>1</v>
+      </c>
+      <c r="G19" s="2">
+        <v>0</v>
+      </c>
+      <c r="H19" s="2">
+        <v>0</v>
+      </c>
+      <c r="I19" s="2">
+        <v>0</v>
+      </c>
+      <c r="J19" s="2">
+        <v>0</v>
+      </c>
+      <c r="K19" s="2">
+        <v>1</v>
+      </c>
+      <c r="L19" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="M19" s="5" t="s">
+        <v>108</v>
+      </c>
+      <c r="N19" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="O19" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="P19" s="2" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="20" customHeight="1" spans="3:16">
+      <c r="C20" s="2">
+        <v>52003</v>
+      </c>
+      <c r="D20" s="2">
+        <v>502</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="F20" s="2">
+        <v>1</v>
+      </c>
+      <c r="G20" s="2">
+        <v>0</v>
+      </c>
+      <c r="H20" s="2">
+        <v>0</v>
+      </c>
+      <c r="I20" s="2">
+        <v>0</v>
+      </c>
+      <c r="J20" s="2">
+        <v>0</v>
+      </c>
+      <c r="K20" s="2">
+        <v>1</v>
+      </c>
+      <c r="L20" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="M20" s="5" t="s">
+        <v>108</v>
+      </c>
+      <c r="N20" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="O20" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="P20" s="2" t="s">
+        <v>111</v>
+      </c>
+    </row>
+  </sheetData>
+  <dataValidations count="1">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:P5" errorStyle="warning">
+      <formula1>COUNTIF($C:$C,C3)&lt;2</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+  <legacyDrawing r:id="rId2"/>
+</worksheet>
 </file>
--- a/Excel/AchievementConfig.xlsx
+++ b/Excel/AchievementConfig.xlsx
@@ -175,7 +175,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="253" uniqueCount="112">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="253" uniqueCount="113">
   <si>
     <t>#</t>
   </si>
@@ -282,21 +282,21 @@
     <t>万法精通</t>
   </si>
   <si>
+    <t>11,93</t>
+  </si>
+  <si>
+    <t>人物学习{0}个技能</t>
+  </si>
+  <si>
+    <t>10 技能数量</t>
+  </si>
+  <si>
+    <t>技能大师</t>
+  </si>
+  <si>
     <t>10,93</t>
   </si>
   <si>
-    <t>人物学习{0}个技能</t>
-  </si>
-  <si>
-    <t>10 技能数量</t>
-  </si>
-  <si>
-    <t>技能大师</t>
-  </si>
-  <si>
-    <t>11,93</t>
-  </si>
-  <si>
     <t>技能总等级达到{0}</t>
   </si>
   <si>
@@ -390,6 +390,9 @@
     <t>BOSS杀手</t>
   </si>
   <si>
+    <t>2001,93</t>
+  </si>
+  <si>
     <t>击杀普通BOSS{0}个</t>
   </si>
   <si>
@@ -423,28 +426,28 @@
     <t>我要输出</t>
   </si>
   <si>
+    <t>3,1003</t>
+  </si>
+  <si>
+    <t>200,2</t>
+  </si>
+  <si>
+    <t>增加攻击</t>
+  </si>
+  <si>
+    <t>我不想死</t>
+  </si>
+  <si>
     <t>2,1002</t>
   </si>
   <si>
-    <t>200,2</t>
-  </si>
-  <si>
-    <t>增加攻击</t>
-  </si>
-  <si>
-    <t>我不想死</t>
-  </si>
-  <si>
-    <t>3,1003</t>
-  </si>
-  <si>
     <t>增加防御</t>
   </si>
   <si>
     <t>给点钱把</t>
   </si>
   <si>
-    <t>81,85</t>
+    <t>85,81</t>
   </si>
   <si>
     <t>增加杀敌金币</t>
@@ -453,7 +456,7 @@
     <t>我想升级</t>
   </si>
   <si>
-    <t>82,86</t>
+    <t>86,82</t>
   </si>
   <si>
     <t>增加杀敌经验</t>
@@ -2362,7 +2365,7 @@
         <v>1</v>
       </c>
       <c r="L36" s="4" t="s">
-        <v>56</v>
+        <v>71</v>
       </c>
       <c r="M36" s="4" t="s">
         <v>21</v>
@@ -2371,7 +2374,7 @@
         <v>21</v>
       </c>
       <c r="O36" s="2" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="P36" s="1" t="s">
         <v>70</v>
@@ -2385,7 +2388,7 @@
         <v>307</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F37" s="2">
         <v>10</v>
@@ -2415,10 +2418,10 @@
         <v>21</v>
       </c>
       <c r="O37" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="P37" s="1" t="s">
         <v>73</v>
-      </c>
-      <c r="P37" s="1" t="s">
-        <v>72</v>
       </c>
     </row>
     <row r="38" customHeight="1" spans="3:16">
@@ -2438,7 +2441,7 @@
         <v>401</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="F42" s="2">
         <v>10</v>
@@ -2468,7 +2471,7 @@
         <v>21</v>
       </c>
       <c r="O42" s="2" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
   </sheetData>
@@ -2649,7 +2652,7 @@
         <v>501</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F6" s="2">
         <v>10</v>
@@ -2670,19 +2673,19 @@
         <v>1</v>
       </c>
       <c r="L6" s="5" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="M6" s="5" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="N6" s="5" t="s">
         <v>31</v>
       </c>
       <c r="O6" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="P6" s="2" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="7" s="2" customFormat="1" customHeight="1" spans="3:16">
@@ -2693,7 +2696,7 @@
         <v>501</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F7" s="2">
         <v>10</v>
@@ -2714,19 +2717,19 @@
         <v>1</v>
       </c>
       <c r="L7" s="5" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="M7" s="5" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="N7" s="5" t="s">
         <v>31</v>
       </c>
       <c r="O7" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="P7" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="8" s="2" customFormat="1" customHeight="1" spans="3:16">
@@ -2737,7 +2740,7 @@
         <v>501</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="F8" s="2">
         <v>10</v>
@@ -2758,19 +2761,19 @@
         <v>1</v>
       </c>
       <c r="L8" s="5" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="M8" s="5" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="N8" s="5" t="s">
         <v>31</v>
       </c>
       <c r="O8" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="P8" s="2" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="9" s="2" customFormat="1" customHeight="1" spans="3:16">
@@ -2781,7 +2784,7 @@
         <v>501</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="F9" s="2">
         <v>10</v>
@@ -2802,19 +2805,19 @@
         <v>1</v>
       </c>
       <c r="L9" s="5" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="M9" s="5" t="s">
-        <v>46</v>
+        <v>31</v>
       </c>
       <c r="N9" s="5" t="s">
         <v>21</v>
       </c>
       <c r="O9" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="P9" s="2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="10" s="2" customFormat="1" customHeight="1" spans="3:16">
@@ -2825,7 +2828,7 @@
         <v>501</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="F10" s="2">
         <v>10</v>
@@ -2846,19 +2849,19 @@
         <v>1</v>
       </c>
       <c r="L10" s="5" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="M10" s="5" t="s">
-        <v>46</v>
+        <v>31</v>
       </c>
       <c r="N10" s="5" t="s">
         <v>21</v>
       </c>
       <c r="O10" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="P10" s="2" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="11" s="2" customFormat="1" customHeight="1" spans="3:16">
@@ -2869,7 +2872,7 @@
         <v>501</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="F11" s="2">
         <v>10</v>
@@ -2890,7 +2893,7 @@
         <v>1</v>
       </c>
       <c r="L11" s="5" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="M11" s="5" t="s">
         <v>21</v>
@@ -2899,10 +2902,10 @@
         <v>21</v>
       </c>
       <c r="O11" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="P11" s="2" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="12" s="2" customFormat="1" customHeight="1" spans="3:16">
@@ -2913,7 +2916,7 @@
         <v>501</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="F12" s="2">
         <v>10</v>
@@ -2934,7 +2937,7 @@
         <v>1</v>
       </c>
       <c r="L12" s="5" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="M12" s="5" t="s">
         <v>21</v>
@@ -2943,10 +2946,10 @@
         <v>21</v>
       </c>
       <c r="O12" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="P12" s="2" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="13" s="2" customFormat="1" customHeight="1" spans="3:16">
@@ -2957,7 +2960,7 @@
         <v>501</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F13" s="2">
         <v>10</v>
@@ -2978,7 +2981,7 @@
         <v>1</v>
       </c>
       <c r="L13" s="5" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="M13" s="5" t="s">
         <v>21</v>
@@ -2987,10 +2990,10 @@
         <v>21</v>
       </c>
       <c r="O13" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="P13" s="2" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="18" s="2" customFormat="1" customHeight="1" spans="3:16">
@@ -3001,7 +3004,7 @@
         <v>502</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="F18" s="2">
         <v>1</v>
@@ -3022,19 +3025,19 @@
         <v>1</v>
       </c>
       <c r="L18" s="5" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="M18" s="5" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="N18" s="5" t="s">
         <v>31</v>
       </c>
       <c r="O18" s="2" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="P18" s="2" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="19" customHeight="1" spans="3:16">
@@ -3045,7 +3048,7 @@
         <v>502</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="F19" s="2">
         <v>1</v>
@@ -3066,19 +3069,19 @@
         <v>1</v>
       </c>
       <c r="L19" s="5" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="M19" s="5" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="N19" s="5" t="s">
         <v>31</v>
       </c>
       <c r="O19" s="2" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="P19" s="2" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="20" customHeight="1" spans="3:16">
@@ -3089,7 +3092,7 @@
         <v>502</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="F20" s="2">
         <v>1</v>
@@ -3110,19 +3113,19 @@
         <v>1</v>
       </c>
       <c r="L20" s="5" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="M20" s="5" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="N20" s="5" t="s">
         <v>31</v>
       </c>
       <c r="O20" s="2" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="P20" s="2" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/AchievementConfig.xlsx
+++ b/Excel/AchievementConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17680"/>
+    <workbookView windowHeight="17680" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="属性奖励" sheetId="1" r:id="rId1"/>
@@ -507,7 +507,7 @@
     <t>500,5</t>
   </si>
   <si>
-    <t>死亡100次</t>
+    <t>死亡666次</t>
   </si>
   <si>
     <t>全职大师</t>

--- a/Excel/AchievementConfig.xlsx
+++ b/Excel/AchievementConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17680" activeTab="1"/>
+    <workbookView windowHeight="17680"/>
   </bookViews>
   <sheets>
     <sheet name="属性奖励" sheetId="1" r:id="rId1"/>
@@ -58,7 +58,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="K3" authorId="1">
+    <comment ref="J3" authorId="1">
       <text>
         <r>
           <rPr>
@@ -175,7 +175,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="253" uniqueCount="113">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="250" uniqueCount="113">
   <si>
     <t>#</t>
   </si>
@@ -201,211 +201,211 @@
     <t>ConRiseType</t>
   </si>
   <si>
+    <t>RewardType</t>
+  </si>
+  <si>
+    <t>AtrIdList</t>
+  </si>
+  <si>
+    <t>AtrVueList</t>
+  </si>
+  <si>
+    <t>AtrRiseTypeList</t>
+  </si>
+  <si>
+    <t>Memo</t>
+  </si>
+  <si>
+    <t>Id</t>
+  </si>
+  <si>
+    <t>int</t>
+  </si>
+  <si>
+    <t>string</t>
+  </si>
+  <si>
+    <t>long</t>
+  </si>
+  <si>
+    <t>int[]</t>
+  </si>
+  <si>
+    <t>超越自我</t>
+  </si>
+  <si>
+    <t>2001,93</t>
+  </si>
+  <si>
+    <t>1,1</t>
+  </si>
+  <si>
+    <t>人物达到{0}级</t>
+  </si>
+  <si>
+    <t>1 人物等级</t>
+  </si>
+  <si>
+    <t>日复一日</t>
+  </si>
+  <si>
+    <t>1001,93</t>
+  </si>
+  <si>
+    <t>游戏天数{0}天</t>
+  </si>
+  <si>
+    <t>2游戏天数</t>
+  </si>
+  <si>
+    <t>用爱发电</t>
+  </si>
+  <si>
+    <t>3,93</t>
+  </si>
+  <si>
+    <t>50,1</t>
+  </si>
+  <si>
+    <t>2,1</t>
+  </si>
+  <si>
+    <t>累计看广告数量{0}个</t>
+  </si>
+  <si>
+    <t>3广告数量</t>
+  </si>
+  <si>
+    <t>万法精通</t>
+  </si>
+  <si>
+    <t>10,93</t>
+  </si>
+  <si>
+    <t>人物学习{0}个技能</t>
+  </si>
+  <si>
+    <t>10 技能数量</t>
+  </si>
+  <si>
+    <t>技能大师</t>
+  </si>
+  <si>
+    <t>11,93</t>
+  </si>
+  <si>
+    <t>技能基础总等级达到{0}</t>
+  </si>
+  <si>
+    <t>11 技能总等级</t>
+  </si>
+  <si>
+    <t>驯兽大师</t>
+  </si>
+  <si>
+    <t>累计获取{0}个宠物</t>
+  </si>
+  <si>
+    <t>101 宠物获取数量</t>
+  </si>
+  <si>
+    <t>装备大师</t>
+  </si>
+  <si>
+    <t>10,1</t>
+  </si>
+  <si>
+    <t>累计获取{0}个装备</t>
+  </si>
+  <si>
+    <t>装备精炼</t>
+  </si>
+  <si>
+    <t>1003,93</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 精炼总等级{0}</t>
+  </si>
+  <si>
+    <t>装备强化</t>
+  </si>
+  <si>
+    <t>强化总等级{0}</t>
+  </si>
+  <si>
+    <t>传世备强化</t>
+  </si>
+  <si>
+    <t>27,93</t>
+  </si>
+  <si>
+    <t>传世强化总等级{0}</t>
+  </si>
+  <si>
+    <t>巅峰之路</t>
+  </si>
+  <si>
+    <t>2003,93</t>
+  </si>
+  <si>
+    <t>主线副本通过{0}关</t>
+  </si>
+  <si>
+    <t>通关副本</t>
+  </si>
+  <si>
+    <t>小怪杀手</t>
+  </si>
+  <si>
+    <t>1,93</t>
+  </si>
+  <si>
+    <t>500,1</t>
+  </si>
+  <si>
+    <t>击杀小怪{0}个</t>
+  </si>
+  <si>
+    <t>精英杀手</t>
+  </si>
+  <si>
+    <t>2,93</t>
+  </si>
+  <si>
+    <t>击杀精英{0}个</t>
+  </si>
+  <si>
+    <t>头目杀手</t>
+  </si>
+  <si>
+    <t>击杀头目{0}个</t>
+  </si>
+  <si>
+    <t>首领杀手</t>
+  </si>
+  <si>
+    <t>击杀首领{0}个</t>
+  </si>
+  <si>
+    <t>BOSS杀手</t>
+  </si>
+  <si>
+    <t>击杀普通BOSS{0}个</t>
+  </si>
+  <si>
+    <t>区域杀手</t>
+  </si>
+  <si>
+    <t>击杀区域BOSS{0}个</t>
+  </si>
+  <si>
+    <t>龙城守护者</t>
+  </si>
+  <si>
+    <t>通关守卫龙城{0}层</t>
+  </si>
+  <si>
     <t>CondRiseVue</t>
-  </si>
-  <si>
-    <t>RewardType</t>
-  </si>
-  <si>
-    <t>AtrIdList</t>
-  </si>
-  <si>
-    <t>AtrVueList</t>
-  </si>
-  <si>
-    <t>AtrRiseTypeList</t>
-  </si>
-  <si>
-    <t>Memo</t>
-  </si>
-  <si>
-    <t>Id</t>
-  </si>
-  <si>
-    <t>int</t>
-  </si>
-  <si>
-    <t>string</t>
-  </si>
-  <si>
-    <t>long</t>
-  </si>
-  <si>
-    <t>int[]</t>
-  </si>
-  <si>
-    <t>超越自我</t>
-  </si>
-  <si>
-    <t>1003,93</t>
-  </si>
-  <si>
-    <t>1,1</t>
-  </si>
-  <si>
-    <t>人物达到{0}级</t>
-  </si>
-  <si>
-    <t>1 人物等级</t>
-  </si>
-  <si>
-    <t>日复一日</t>
-  </si>
-  <si>
-    <t>1001,93</t>
-  </si>
-  <si>
-    <t>游戏天数{0}天</t>
-  </si>
-  <si>
-    <t>2游戏天数</t>
-  </si>
-  <si>
-    <t>用爱发电</t>
-  </si>
-  <si>
-    <t>3,93</t>
-  </si>
-  <si>
-    <t>50,1</t>
-  </si>
-  <si>
-    <t>2,1</t>
-  </si>
-  <si>
-    <t>累计看广告数量{0}个</t>
-  </si>
-  <si>
-    <t>3广告数量</t>
-  </si>
-  <si>
-    <t>万法精通</t>
-  </si>
-  <si>
-    <t>11,93</t>
-  </si>
-  <si>
-    <t>人物学习{0}个技能</t>
-  </si>
-  <si>
-    <t>10 技能数量</t>
-  </si>
-  <si>
-    <t>技能大师</t>
-  </si>
-  <si>
-    <t>10,93</t>
-  </si>
-  <si>
-    <t>技能总等级达到{0}</t>
-  </si>
-  <si>
-    <t>11 技能总等级</t>
-  </si>
-  <si>
-    <t>驯兽大师</t>
-  </si>
-  <si>
-    <t>累计获取{0}个宠物</t>
-  </si>
-  <si>
-    <t>101 宠物获取数量</t>
-  </si>
-  <si>
-    <t>装备大师</t>
-  </si>
-  <si>
-    <t>10,1</t>
-  </si>
-  <si>
-    <t>累计获取{0}个装备</t>
-  </si>
-  <si>
-    <t>装备精炼</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 精炼总等级{0}</t>
-  </si>
-  <si>
-    <t>装备强化</t>
-  </si>
-  <si>
-    <t>强化总等级{0}</t>
-  </si>
-  <si>
-    <t>传世备强化</t>
-  </si>
-  <si>
-    <t>27,93</t>
-  </si>
-  <si>
-    <t>传世强化总等级{0}</t>
-  </si>
-  <si>
-    <t>巅峰之路</t>
-  </si>
-  <si>
-    <t>2003,93</t>
-  </si>
-  <si>
-    <t>主线副本通过{0}关</t>
-  </si>
-  <si>
-    <t>通关副本</t>
-  </si>
-  <si>
-    <t>小怪杀手</t>
-  </si>
-  <si>
-    <t>1,93</t>
-  </si>
-  <si>
-    <t>500,1</t>
-  </si>
-  <si>
-    <t>击杀小怪{0}个</t>
-  </si>
-  <si>
-    <t>精英杀手</t>
-  </si>
-  <si>
-    <t>2,93</t>
-  </si>
-  <si>
-    <t>击杀精英{0}个</t>
-  </si>
-  <si>
-    <t>头目杀手</t>
-  </si>
-  <si>
-    <t>击杀头目{0}个</t>
-  </si>
-  <si>
-    <t>首领杀手</t>
-  </si>
-  <si>
-    <t>击杀首领{0}个</t>
-  </si>
-  <si>
-    <t>BOSS杀手</t>
-  </si>
-  <si>
-    <t>2001,93</t>
-  </si>
-  <si>
-    <t>击杀普通BOSS{0}个</t>
-  </si>
-  <si>
-    <t>区域杀手</t>
-  </si>
-  <si>
-    <t>击杀区域BOSS{0}个</t>
-  </si>
-  <si>
-    <t>龙城守护者</t>
-  </si>
-  <si>
-    <t>通关守卫龙城{0}层</t>
   </si>
   <si>
     <t>保护脆皮</t>
@@ -1485,33 +1485,33 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C1:P42"/>
+  <dimension ref="C1:O42"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16" customHeight="1"/>
   <cols>
     <col min="1" max="3" width="9" style="2"/>
     <col min="4" max="4" width="11.5454545454545" style="2" customWidth="1"/>
     <col min="5" max="5" width="15.0909090909091" style="2" customWidth="1"/>
-    <col min="6" max="10" width="16.8181818181818" style="2" customWidth="1"/>
-    <col min="11" max="11" width="15.1818181818182" style="2" customWidth="1"/>
-    <col min="12" max="12" width="13.9090909090909" style="2" customWidth="1"/>
-    <col min="13" max="13" width="13.7272727272727" style="2" customWidth="1"/>
-    <col min="14" max="14" width="16.6363636363636" style="2" customWidth="1"/>
-    <col min="15" max="15" width="22.2727272727273" style="2" customWidth="1"/>
-    <col min="16" max="16" width="21" style="2" customWidth="1"/>
-    <col min="17" max="16384" width="9" style="2"/>
+    <col min="6" max="9" width="16.8181818181818" style="2" customWidth="1"/>
+    <col min="10" max="10" width="15.1818181818182" style="2" customWidth="1"/>
+    <col min="11" max="11" width="13.9090909090909" style="2" customWidth="1"/>
+    <col min="12" max="12" width="13.7272727272727" style="2" customWidth="1"/>
+    <col min="13" max="13" width="16.6363636363636" style="2" customWidth="1"/>
+    <col min="14" max="14" width="22.2727272727273" style="2" customWidth="1"/>
+    <col min="15" max="15" width="21" style="2" customWidth="1"/>
+    <col min="16" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" customHeight="1" spans="3:16">
-      <c r="P1" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="2" s="1" customFormat="1" customHeight="1" spans="3:16">
-      <c r="P2" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" s="1" customFormat="1" customHeight="1" spans="3:16">
+    <row r="1" s="1" customFormat="1" customHeight="1" spans="3:15">
+      <c r="O1" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" s="1" customFormat="1" customHeight="1" spans="3:15">
+      <c r="O2" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" s="1" customFormat="1" customHeight="1" spans="3:15">
       <c r="C3" s="3" t="s">
         <v>1</v>
       </c>
@@ -1549,15 +1549,12 @@
         <v>12</v>
       </c>
       <c r="O3" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" s="1" customFormat="1" customHeight="1" spans="3:15">
+      <c r="C4" s="3" t="s">
         <v>13</v>
-      </c>
-      <c r="P3" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="4" s="1" customFormat="1" customHeight="1" spans="3:16">
-      <c r="C4" s="3" t="s">
-        <v>14</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>2</v>
@@ -1592,54 +1589,48 @@
       <c r="N4" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="O4" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="P4" s="3"/>
-    </row>
-    <row r="5" s="1" customFormat="1" customHeight="1" spans="3:16">
+      <c r="O4" s="3"/>
+    </row>
+    <row r="5" s="1" customFormat="1" customHeight="1" spans="3:15">
       <c r="C5" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E5" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="D5" s="3" t="s">
+      <c r="F5" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I5" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="J5" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="K5" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="L5" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="M5" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="N5" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="E5" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="F5" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="G5" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="H5" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="I5" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="J5" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="K5" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="L5" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="M5" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="N5" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="O5" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="P5" s="3"/>
-    </row>
-    <row r="6" customHeight="1" spans="3:16">
+      <c r="O5" s="3"/>
+    </row>
+    <row r="6" customHeight="1" spans="3:15">
       <c r="C6" s="2">
         <v>1</v>
       </c>
@@ -1647,7 +1638,7 @@
         <v>101</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F6" s="1">
         <v>10</v>
@@ -1662,28 +1653,25 @@
         <v>1</v>
       </c>
       <c r="J6" s="1">
-        <v>10</v>
-      </c>
-      <c r="K6" s="1">
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="K6" s="4" t="s">
+        <v>19</v>
       </c>
       <c r="L6" s="4" t="s">
         <v>20</v>
       </c>
       <c r="M6" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="N6" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="N6" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="O6" s="1" t="s">
+      <c r="O6" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="P6" s="3" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="7" customHeight="1" spans="3:16">
+    </row>
+    <row r="7" customHeight="1" spans="3:15">
       <c r="C7" s="2">
         <v>2</v>
       </c>
@@ -1691,7 +1679,7 @@
         <v>101</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F7" s="2">
         <v>30</v>
@@ -1705,29 +1693,26 @@
       <c r="I7" s="2">
         <v>1</v>
       </c>
-      <c r="J7" s="2">
-        <v>3</v>
-      </c>
-      <c r="K7" s="1">
-        <v>1</v>
+      <c r="J7" s="1">
+        <v>1</v>
+      </c>
+      <c r="K7" s="4" t="s">
+        <v>24</v>
       </c>
       <c r="L7" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="M7" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="N7" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="M7" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="N7" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="O7" s="2" t="s">
+      <c r="O7" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="P7" s="3" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="8" customHeight="1" spans="3:16">
+    </row>
+    <row r="8" customHeight="1" spans="3:15">
       <c r="C8" s="2">
         <v>3</v>
       </c>
@@ -1735,7 +1720,7 @@
         <v>101</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F8" s="2">
         <v>30</v>
@@ -1750,10 +1735,10 @@
         <v>1</v>
       </c>
       <c r="J8" s="2">
-        <v>6</v>
-      </c>
-      <c r="K8" s="2">
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="K8" s="4" t="s">
+        <v>28</v>
       </c>
       <c r="L8" s="4" t="s">
         <v>29</v>
@@ -1761,23 +1746,20 @@
       <c r="M8" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="N8" s="4" t="s">
+      <c r="N8" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="O8" s="2" t="s">
+      <c r="O8" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="P8" s="3" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="9" customHeight="1" spans="3:16">
-      <c r="P9" s="3"/>
-    </row>
-    <row r="10" customHeight="1" spans="3:16">
-      <c r="P10" s="3"/>
-    </row>
-    <row r="11" customHeight="1" spans="3:16">
+    </row>
+    <row r="9" customHeight="1" spans="3:15">
+      <c r="O9" s="3"/>
+    </row>
+    <row r="10" customHeight="1" spans="3:15">
+      <c r="O10" s="3"/>
+    </row>
+    <row r="11" customHeight="1" spans="3:15">
       <c r="C11" s="2">
         <v>10001</v>
       </c>
@@ -1785,7 +1767,7 @@
         <v>102</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F11" s="2">
         <v>10</v>
@@ -1800,28 +1782,25 @@
         <v>1</v>
       </c>
       <c r="J11" s="2">
-        <v>3</v>
-      </c>
-      <c r="K11" s="2">
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="K11" s="4" t="s">
+        <v>34</v>
       </c>
       <c r="L11" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="M11" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="N11" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="M11" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="N11" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="O11" s="1" t="s">
+      <c r="O11" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="P11" s="3" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="12" customHeight="1" spans="3:16">
+    </row>
+    <row r="12" customHeight="1" spans="3:15">
       <c r="C12" s="2">
         <v>10002</v>
       </c>
@@ -1829,7 +1808,7 @@
         <v>102</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F12" s="2">
         <v>10</v>
@@ -1838,37 +1817,34 @@
         <v>11</v>
       </c>
       <c r="H12" s="2">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="I12" s="2">
         <v>1</v>
       </c>
       <c r="J12" s="2">
-        <v>10</v>
-      </c>
-      <c r="K12" s="2">
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="K12" s="4" t="s">
+        <v>38</v>
       </c>
       <c r="L12" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="M12" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="N12" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="M12" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="N12" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="O12" s="1" t="s">
+      <c r="O12" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="P12" s="3" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="13" customHeight="1" spans="3:16">
-      <c r="P13" s="3"/>
-    </row>
-    <row r="14" customHeight="1" spans="3:16">
+    </row>
+    <row r="13" customHeight="1" spans="3:15">
+      <c r="O13" s="3"/>
+    </row>
+    <row r="14" customHeight="1" spans="3:15">
       <c r="C14" s="2">
         <v>103001</v>
       </c>
@@ -1876,7 +1852,7 @@
         <v>103</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F14" s="2">
         <v>10</v>
@@ -1885,16 +1861,16 @@
         <v>101</v>
       </c>
       <c r="H14" s="2">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="I14" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J14" s="2">
-        <v>100</v>
-      </c>
-      <c r="K14" s="2">
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="K14" s="4" t="s">
+        <v>28</v>
       </c>
       <c r="L14" s="4" t="s">
         <v>29</v>
@@ -1902,47 +1878,44 @@
       <c r="M14" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="N14" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="O14" s="1" t="s">
+      <c r="N14" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="O14" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="P14" s="3" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="15" customHeight="1" spans="3:16">
-      <c r="P15" s="3"/>
-    </row>
-    <row r="16" customHeight="1" spans="3:16">
-      <c r="P16" s="3"/>
-    </row>
-    <row r="17" customHeight="1" spans="3:16">
-      <c r="P17" s="3"/>
-    </row>
-    <row r="18" customHeight="1" spans="3:16">
-      <c r="P18" s="3"/>
-    </row>
-    <row r="19" customHeight="1" spans="3:16">
-      <c r="P19" s="3"/>
-    </row>
-    <row r="20" customHeight="1" spans="3:16">
-      <c r="P20" s="3"/>
-    </row>
-    <row r="21" customHeight="1" spans="3:16">
-      <c r="P21" s="3"/>
-    </row>
-    <row r="22" customHeight="1" spans="3:16">
-      <c r="P22" s="3"/>
-    </row>
-    <row r="23" customHeight="1" spans="3:16">
-      <c r="P23" s="3"/>
-    </row>
-    <row r="24" customHeight="1" spans="3:16">
-      <c r="P24" s="3"/>
-    </row>
-    <row r="25" customHeight="1" spans="3:16">
+    </row>
+    <row r="15" customHeight="1" spans="3:15">
+      <c r="O15" s="3"/>
+    </row>
+    <row r="16" customHeight="1" spans="3:15">
+      <c r="O16" s="3"/>
+    </row>
+    <row r="17" customHeight="1" spans="3:15">
+      <c r="O17" s="3"/>
+    </row>
+    <row r="18" customHeight="1" spans="3:15">
+      <c r="O18" s="3"/>
+    </row>
+    <row r="19" customHeight="1" spans="3:15">
+      <c r="O19" s="3"/>
+    </row>
+    <row r="20" customHeight="1" spans="3:15">
+      <c r="O20" s="3"/>
+    </row>
+    <row r="21" customHeight="1" spans="3:15">
+      <c r="O21" s="3"/>
+    </row>
+    <row r="22" customHeight="1" spans="3:15">
+      <c r="O22" s="3"/>
+    </row>
+    <row r="23" customHeight="1" spans="3:15">
+      <c r="O23" s="3"/>
+    </row>
+    <row r="24" customHeight="1" spans="3:15">
+      <c r="O24" s="3"/>
+    </row>
+    <row r="25" customHeight="1" spans="3:15">
       <c r="C25" s="2">
         <v>201001</v>
       </c>
@@ -1950,7 +1923,7 @@
         <v>201</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F25" s="2">
         <v>30</v>
@@ -1962,29 +1935,26 @@
         <v>1000</v>
       </c>
       <c r="I25" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J25" s="2">
-        <v>0</v>
-      </c>
-      <c r="K25" s="2">
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="K25" s="4" t="s">
+        <v>28</v>
       </c>
       <c r="L25" s="4" t="s">
-        <v>29</v>
+        <v>45</v>
       </c>
       <c r="M25" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="N25" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="N25" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="O25" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="P25" s="3"/>
-    </row>
-    <row r="26" customHeight="1" spans="3:16">
+      <c r="O25" s="3"/>
+    </row>
+    <row r="26" customHeight="1" spans="3:15">
       <c r="C26" s="2">
         <v>202001</v>
       </c>
@@ -1992,7 +1962,7 @@
         <v>202</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F26" s="2">
         <v>30</v>
@@ -2007,26 +1977,23 @@
         <v>1</v>
       </c>
       <c r="J26" s="2">
-        <v>10</v>
-      </c>
-      <c r="K26" s="2">
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="K26" s="4" t="s">
+        <v>48</v>
       </c>
       <c r="L26" s="4" t="s">
         <v>20</v>
       </c>
       <c r="M26" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="N26" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="O26" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="N26" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="P26" s="3"/>
-    </row>
-    <row r="27" customHeight="1" spans="3:16">
+      <c r="O26" s="3"/>
+    </row>
+    <row r="27" customHeight="1" spans="3:15">
       <c r="C27" s="2">
         <v>203001</v>
       </c>
@@ -2049,26 +2016,23 @@
         <v>1</v>
       </c>
       <c r="J27" s="2">
-        <v>10</v>
-      </c>
-      <c r="K27" s="2">
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="K27" s="4" t="s">
+        <v>48</v>
       </c>
       <c r="L27" s="4" t="s">
         <v>20</v>
       </c>
       <c r="M27" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="N27" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="O27" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="N27" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="P27" s="3"/>
-    </row>
-    <row r="28" customHeight="1" spans="3:16">
+      <c r="O27" s="3"/>
+    </row>
+    <row r="28" customHeight="1" spans="3:15">
       <c r="C28" s="2">
         <v>203002</v>
       </c>
@@ -2091,32 +2055,29 @@
         <v>1</v>
       </c>
       <c r="J28" s="2">
-        <v>24</v>
-      </c>
-      <c r="K28" s="2">
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="K28" s="4" t="s">
+        <v>53</v>
       </c>
       <c r="L28" s="4" t="s">
-        <v>53</v>
+        <v>20</v>
       </c>
       <c r="M28" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="N28" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="O28" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="N28" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="P28" s="3"/>
-    </row>
-    <row r="29" customHeight="1" spans="3:16">
-      <c r="P29" s="3"/>
-    </row>
-    <row r="30" customHeight="1" spans="3:16">
-      <c r="P30" s="3"/>
-    </row>
-    <row r="31" customHeight="1" spans="3:16">
+      <c r="O28" s="3"/>
+    </row>
+    <row r="29" customHeight="1" spans="3:15">
+      <c r="O29" s="3"/>
+    </row>
+    <row r="30" customHeight="1" spans="3:15">
+      <c r="O30" s="3"/>
+    </row>
+    <row r="31" customHeight="1" spans="3:15">
       <c r="C31" s="2">
         <v>30001</v>
       </c>
@@ -2141,26 +2102,23 @@
       <c r="J31" s="2">
         <v>1</v>
       </c>
-      <c r="K31" s="2">
-        <v>1</v>
+      <c r="K31" s="4" t="s">
+        <v>56</v>
       </c>
       <c r="L31" s="4" t="s">
-        <v>56</v>
+        <v>20</v>
       </c>
       <c r="M31" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="N31" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="O31" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="N31" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="P31" s="1" t="s">
+      <c r="O31" s="1" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="32" customHeight="1" spans="3:16">
+    <row r="32" customHeight="1" spans="3:15">
       <c r="C32" s="2">
         <v>30002</v>
       </c>
@@ -2180,31 +2138,28 @@
         <v>100000</v>
       </c>
       <c r="I32" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J32" s="2">
-        <v>0</v>
-      </c>
-      <c r="K32" s="2">
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="K32" s="4" t="s">
+        <v>60</v>
       </c>
       <c r="L32" s="4" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="M32" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="N32" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="O32" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="N32" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="P32" s="1" t="s">
+      <c r="O32" s="1" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="33" customHeight="1" spans="3:16">
+    <row r="33" customHeight="1" spans="3:15">
       <c r="C33" s="2">
         <v>30003</v>
       </c>
@@ -2224,31 +2179,28 @@
         <v>10000</v>
       </c>
       <c r="I33" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J33" s="2">
-        <v>0</v>
-      </c>
-      <c r="K33" s="2">
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="K33" s="4" t="s">
+        <v>64</v>
       </c>
       <c r="L33" s="4" t="s">
-        <v>64</v>
+        <v>29</v>
       </c>
       <c r="M33" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="N33" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="O33" s="2" t="s">
+      <c r="N33" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="P33" s="1" t="s">
+      <c r="O33" s="1" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="34" customHeight="1" spans="3:16">
+    <row r="34" customHeight="1" spans="3:15">
       <c r="C34" s="2">
         <v>30004</v>
       </c>
@@ -2265,16 +2217,16 @@
         <v>304</v>
       </c>
       <c r="H34" s="2">
-        <v>1000</v>
+        <v>2000</v>
       </c>
       <c r="I34" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J34" s="2">
-        <v>0</v>
-      </c>
-      <c r="K34" s="2">
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="K34" s="4" t="s">
+        <v>28</v>
       </c>
       <c r="L34" s="4" t="s">
         <v>29</v>
@@ -2282,17 +2234,14 @@
       <c r="M34" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="N34" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="O34" s="2" t="s">
+      <c r="N34" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="P34" s="1" t="s">
+      <c r="O34" s="1" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="35" customHeight="1" spans="3:16">
+    <row r="35" customHeight="1" spans="3:15">
       <c r="C35" s="2">
         <v>30005</v>
       </c>
@@ -2309,34 +2258,31 @@
         <v>305</v>
       </c>
       <c r="H35" s="2">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="I35" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J35" s="2">
-        <v>0</v>
-      </c>
-      <c r="K35" s="2">
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="K35" s="4" t="s">
+        <v>48</v>
       </c>
       <c r="L35" s="4" t="s">
         <v>20</v>
       </c>
       <c r="M35" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="N35" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="O35" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="N35" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="P35" s="1" t="s">
+      <c r="O35" s="1" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="36" customHeight="1" spans="3:16">
+    <row r="36" customHeight="1" spans="3:15">
       <c r="C36" s="2">
         <v>30006</v>
       </c>
@@ -2353,34 +2299,31 @@
         <v>306</v>
       </c>
       <c r="H36" s="2">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="I36" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J36" s="2">
-        <v>0</v>
-      </c>
-      <c r="K36" s="2">
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="K36" s="4" t="s">
+        <v>19</v>
       </c>
       <c r="L36" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="M36" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="N36" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="M36" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="N36" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="O36" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="P36" s="1" t="s">
+      <c r="O36" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="37" customHeight="1" spans="3:16">
+    <row r="37" customHeight="1" spans="3:15">
       <c r="C37" s="2">
         <v>30007</v>
       </c>
@@ -2388,7 +2331,7 @@
         <v>307</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F37" s="2">
         <v>10</v>
@@ -2397,43 +2340,40 @@
         <v>307</v>
       </c>
       <c r="H37" s="2">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I37" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J37" s="2">
-        <v>0</v>
-      </c>
-      <c r="K37" s="2">
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="K37" s="4" t="s">
+        <v>56</v>
       </c>
       <c r="L37" s="4" t="s">
-        <v>56</v>
+        <v>20</v>
       </c>
       <c r="M37" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="N37" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="O37" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="P37" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="N37" s="2" t="s">
         <v>73</v>
       </c>
-    </row>
-    <row r="38" customHeight="1" spans="3:16">
-      <c r="P38" s="3"/>
-    </row>
-    <row r="39" customHeight="1" spans="3:16">
-      <c r="P39" s="3"/>
-    </row>
-    <row r="40" customHeight="1" spans="3:16">
-      <c r="P40" s="3"/>
-    </row>
-    <row r="42" customHeight="1" spans="3:16">
+      <c r="O37" s="1" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="38" customHeight="1" spans="3:15">
+      <c r="O38" s="3"/>
+    </row>
+    <row r="39" customHeight="1" spans="3:15">
+      <c r="O39" s="3"/>
+    </row>
+    <row r="40" customHeight="1" spans="3:15">
+      <c r="O40" s="3"/>
+    </row>
+    <row r="42" customHeight="1" spans="3:15">
       <c r="C42" s="2">
         <v>40001</v>
       </c>
@@ -2441,7 +2381,7 @@
         <v>401</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F42" s="2">
         <v>10</v>
@@ -2456,27 +2396,24 @@
         <v>1</v>
       </c>
       <c r="J42" s="2">
-        <v>10</v>
-      </c>
-      <c r="K42" s="2">
-        <v>1</v>
-      </c>
-      <c r="L42" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="K42" s="5" t="s">
         <v>53</v>
       </c>
+      <c r="L42" s="4" t="s">
+        <v>20</v>
+      </c>
       <c r="M42" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="N42" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="O42" s="2" t="s">
-        <v>76</v>
+        <v>20</v>
+      </c>
+      <c r="N42" s="2" t="s">
+        <v>75</v>
       </c>
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="P6:P30 P38:P40 C3:P5" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="O6:O30 O38:O40 C3:O5" errorStyle="warning">
       <formula1>COUNTIF($C:$C,C3)&lt;2</formula1>
     </dataValidation>
   </dataValidations>
@@ -2539,22 +2476,22 @@
         <v>7</v>
       </c>
       <c r="J3" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="K3" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K3" s="3" t="s">
+      <c r="L3" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="L3" s="3" t="s">
+      <c r="M3" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="M3" s="3" t="s">
+      <c r="N3" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="N3" s="3" t="s">
+      <c r="O3" s="3" t="s">
         <v>12</v>
-      </c>
-      <c r="O3" s="3" t="s">
-        <v>13</v>
       </c>
       <c r="P3" s="3" t="s">
         <v>5</v>
@@ -2562,7 +2499,7 @@
     </row>
     <row r="4" s="1" customFormat="1" customHeight="1" spans="3:16">
       <c r="C4" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>2</v>
@@ -2583,64 +2520,64 @@
         <v>7</v>
       </c>
       <c r="J4" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="K4" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K4" s="3" t="s">
+      <c r="L4" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="L4" s="3" t="s">
+      <c r="M4" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="M4" s="3" t="s">
+      <c r="N4" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="N4" s="3" t="s">
+      <c r="O4" s="3" t="s">
         <v>12</v>
-      </c>
-      <c r="O4" s="3" t="s">
-        <v>13</v>
       </c>
       <c r="P4" s="3"/>
     </row>
     <row r="5" s="1" customFormat="1" customHeight="1" spans="3:16">
       <c r="C5" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E5" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="D5" s="3" t="s">
+      <c r="F5" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I5" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="J5" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="K5" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="L5" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="M5" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="N5" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="O5" s="3" t="s">
         <v>15</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="F5" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="G5" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="H5" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="I5" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="J5" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="K5" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="L5" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="M5" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="N5" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="O5" s="3" t="s">
-        <v>16</v>
       </c>
       <c r="P5" s="3"/>
     </row>
@@ -2679,7 +2616,7 @@
         <v>79</v>
       </c>
       <c r="N6" s="5" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="O6" s="2" t="s">
         <v>80</v>
@@ -2723,7 +2660,7 @@
         <v>84</v>
       </c>
       <c r="N7" s="5" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="O7" s="2" t="s">
         <v>80</v>
@@ -2767,7 +2704,7 @@
         <v>84</v>
       </c>
       <c r="N8" s="5" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="O8" s="2" t="s">
         <v>80</v>
@@ -2808,10 +2745,10 @@
         <v>90</v>
       </c>
       <c r="M9" s="5" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="N9" s="5" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="O9" s="2" t="s">
         <v>80</v>
@@ -2852,10 +2789,10 @@
         <v>93</v>
       </c>
       <c r="M10" s="5" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="N10" s="5" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="O10" s="2" t="s">
         <v>80</v>
@@ -2896,10 +2833,10 @@
         <v>96</v>
       </c>
       <c r="M11" s="5" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="N11" s="5" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="O11" s="2" t="s">
         <v>80</v>
@@ -2940,10 +2877,10 @@
         <v>99</v>
       </c>
       <c r="M12" s="5" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="N12" s="5" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="O12" s="2" t="s">
         <v>80</v>
@@ -2984,10 +2921,10 @@
         <v>102</v>
       </c>
       <c r="M13" s="5" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="N13" s="5" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="O13" s="2" t="s">
         <v>80</v>
@@ -3031,7 +2968,7 @@
         <v>105</v>
       </c>
       <c r="N18" s="5" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="O18" s="2" t="s">
         <v>106</v>
@@ -3075,7 +3012,7 @@
         <v>109</v>
       </c>
       <c r="N19" s="5" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="O19" s="2" t="s">
         <v>106</v>
@@ -3119,7 +3056,7 @@
         <v>109</v>
       </c>
       <c r="N20" s="5" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="O20" s="2" t="s">
         <v>106</v>

--- a/Excel/AchievementConfig.xlsx
+++ b/Excel/AchievementConfig.xlsx
@@ -175,7 +175,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="250" uniqueCount="113">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="255" uniqueCount="116">
   <si>
     <t>#</t>
   </si>
@@ -324,22 +324,31 @@
     <t>1003,93</t>
   </si>
   <si>
-    <t xml:space="preserve"> 精炼总等级{0}</t>
+    <t xml:space="preserve"> 精炼总等级{0}级</t>
   </si>
   <si>
     <t>装备强化</t>
   </si>
   <si>
-    <t>强化总等级{0}</t>
-  </si>
-  <si>
-    <t>传世备强化</t>
+    <t>1002,93</t>
+  </si>
+  <si>
+    <t>强化总等级{0}级</t>
+  </si>
+  <si>
+    <t>传世强化</t>
   </si>
   <si>
     <t>27,93</t>
   </si>
   <si>
-    <t>传世强化总等级{0}</t>
+    <t>传世强化总等级{0}级</t>
+  </si>
+  <si>
+    <t>四格进阶</t>
+  </si>
+  <si>
+    <t>四格总阶数{0}阶</t>
   </si>
   <si>
     <t>巅峰之路</t>
@@ -2019,7 +2028,7 @@
         <v>1</v>
       </c>
       <c r="K27" s="4" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="L27" s="4" t="s">
         <v>20</v>
@@ -2028,7 +2037,7 @@
         <v>20</v>
       </c>
       <c r="N27" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="O27" s="3"/>
     </row>
@@ -2040,7 +2049,7 @@
         <v>204</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F28" s="2">
         <v>10</v>
@@ -2058,7 +2067,7 @@
         <v>1</v>
       </c>
       <c r="K28" s="4" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="L28" s="4" t="s">
         <v>20</v>
@@ -2067,11 +2076,47 @@
         <v>20</v>
       </c>
       <c r="N28" s="2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="O28" s="3"/>
     </row>
     <row r="29" customHeight="1" spans="3:15">
+      <c r="C29" s="2">
+        <v>203003</v>
+      </c>
+      <c r="D29" s="2">
+        <v>205</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="F29" s="2">
+        <v>20</v>
+      </c>
+      <c r="G29" s="2">
+        <v>205</v>
+      </c>
+      <c r="H29" s="2">
+        <v>4</v>
+      </c>
+      <c r="I29" s="2">
+        <v>1</v>
+      </c>
+      <c r="J29" s="2">
+        <v>1</v>
+      </c>
+      <c r="K29" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="L29" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="M29" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="N29" s="2" t="s">
+        <v>57</v>
+      </c>
       <c r="O29" s="3"/>
     </row>
     <row r="30" customHeight="1" spans="3:15">
@@ -2085,7 +2130,7 @@
         <v>301</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="F31" s="2">
         <v>30</v>
@@ -2103,7 +2148,7 @@
         <v>1</v>
       </c>
       <c r="K31" s="4" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="L31" s="4" t="s">
         <v>20</v>
@@ -2112,10 +2157,10 @@
         <v>20</v>
       </c>
       <c r="N31" s="2" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="O31" s="1" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
     </row>
     <row r="32" customHeight="1" spans="3:15">
@@ -2126,7 +2171,7 @@
         <v>302</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="F32" s="2">
         <v>10</v>
@@ -2144,19 +2189,19 @@
         <v>1</v>
       </c>
       <c r="K32" s="4" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="L32" s="4" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="M32" s="4" t="s">
         <v>30</v>
       </c>
       <c r="N32" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="O32" s="1" t="s">
         <v>62</v>
-      </c>
-      <c r="O32" s="1" t="s">
-        <v>59</v>
       </c>
     </row>
     <row r="33" customHeight="1" spans="3:15">
@@ -2167,7 +2212,7 @@
         <v>303</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="F33" s="2">
         <v>10</v>
@@ -2185,7 +2230,7 @@
         <v>1</v>
       </c>
       <c r="K33" s="4" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="L33" s="4" t="s">
         <v>29</v>
@@ -2194,10 +2239,10 @@
         <v>30</v>
       </c>
       <c r="N33" s="2" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="O33" s="1" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
     </row>
     <row r="34" customHeight="1" spans="3:15">
@@ -2208,7 +2253,7 @@
         <v>304</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="F34" s="2">
         <v>10</v>
@@ -2235,10 +2280,10 @@
         <v>30</v>
       </c>
       <c r="N34" s="2" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="O34" s="1" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
     </row>
     <row r="35" customHeight="1" spans="3:15">
@@ -2249,7 +2294,7 @@
         <v>305</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="F35" s="2">
         <v>10</v>
@@ -2276,10 +2321,10 @@
         <v>20</v>
       </c>
       <c r="N35" s="2" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="O35" s="1" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
     </row>
     <row r="36" customHeight="1" spans="3:15">
@@ -2290,7 +2335,7 @@
         <v>306</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="F36" s="2">
         <v>10</v>
@@ -2317,10 +2362,10 @@
         <v>20</v>
       </c>
       <c r="N36" s="2" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="O36" s="1" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
     </row>
     <row r="37" customHeight="1" spans="3:15">
@@ -2331,7 +2376,7 @@
         <v>307</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="F37" s="2">
         <v>10</v>
@@ -2349,7 +2394,7 @@
         <v>1</v>
       </c>
       <c r="K37" s="4" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="L37" s="4" t="s">
         <v>20</v>
@@ -2358,10 +2403,10 @@
         <v>20</v>
       </c>
       <c r="N37" s="2" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="O37" s="1" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
     </row>
     <row r="38" customHeight="1" spans="3:15">
@@ -2381,7 +2426,7 @@
         <v>401</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="F42" s="2">
         <v>10</v>
@@ -2399,7 +2444,7 @@
         <v>1</v>
       </c>
       <c r="K42" s="5" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="L42" s="4" t="s">
         <v>20</v>
@@ -2408,7 +2453,7 @@
         <v>20</v>
       </c>
       <c r="N42" s="2" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
     </row>
   </sheetData>
@@ -2476,7 +2521,7 @@
         <v>7</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="K3" s="3" t="s">
         <v>8</v>
@@ -2520,7 +2565,7 @@
         <v>7</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="K4" s="3" t="s">
         <v>8</v>
@@ -2589,7 +2634,7 @@
         <v>501</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="F6" s="2">
         <v>10</v>
@@ -2610,19 +2655,19 @@
         <v>1</v>
       </c>
       <c r="L6" s="5" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="M6" s="5" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="N6" s="5" t="s">
         <v>30</v>
       </c>
       <c r="O6" s="2" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="P6" s="2" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
     </row>
     <row r="7" s="2" customFormat="1" customHeight="1" spans="3:16">
@@ -2633,7 +2678,7 @@
         <v>501</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="F7" s="2">
         <v>10</v>
@@ -2654,19 +2699,19 @@
         <v>1</v>
       </c>
       <c r="L7" s="5" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="M7" s="5" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="N7" s="5" t="s">
         <v>30</v>
       </c>
       <c r="O7" s="2" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="P7" s="2" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
     </row>
     <row r="8" s="2" customFormat="1" customHeight="1" spans="3:16">
@@ -2677,7 +2722,7 @@
         <v>501</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="F8" s="2">
         <v>10</v>
@@ -2698,19 +2743,19 @@
         <v>1</v>
       </c>
       <c r="L8" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="M8" s="5" t="s">
         <v>87</v>
-      </c>
-      <c r="M8" s="5" t="s">
-        <v>84</v>
       </c>
       <c r="N8" s="5" t="s">
         <v>30</v>
       </c>
       <c r="O8" s="2" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="P8" s="2" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
     </row>
     <row r="9" s="2" customFormat="1" customHeight="1" spans="3:16">
@@ -2721,7 +2766,7 @@
         <v>501</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="F9" s="2">
         <v>10</v>
@@ -2742,7 +2787,7 @@
         <v>1</v>
       </c>
       <c r="L9" s="5" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="M9" s="5" t="s">
         <v>30</v>
@@ -2751,10 +2796,10 @@
         <v>20</v>
       </c>
       <c r="O9" s="2" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="P9" s="2" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
     </row>
     <row r="10" s="2" customFormat="1" customHeight="1" spans="3:16">
@@ -2765,7 +2810,7 @@
         <v>501</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="F10" s="2">
         <v>10</v>
@@ -2786,7 +2831,7 @@
         <v>1</v>
       </c>
       <c r="L10" s="5" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="M10" s="5" t="s">
         <v>30</v>
@@ -2795,10 +2840,10 @@
         <v>20</v>
       </c>
       <c r="O10" s="2" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="P10" s="2" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
     </row>
     <row r="11" s="2" customFormat="1" customHeight="1" spans="3:16">
@@ -2809,7 +2854,7 @@
         <v>501</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="F11" s="2">
         <v>10</v>
@@ -2830,7 +2875,7 @@
         <v>1</v>
       </c>
       <c r="L11" s="5" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="M11" s="5" t="s">
         <v>20</v>
@@ -2839,10 +2884,10 @@
         <v>20</v>
       </c>
       <c r="O11" s="2" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="P11" s="2" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
     </row>
     <row r="12" s="2" customFormat="1" customHeight="1" spans="3:16">
@@ -2853,7 +2898,7 @@
         <v>501</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="F12" s="2">
         <v>10</v>
@@ -2874,7 +2919,7 @@
         <v>1</v>
       </c>
       <c r="L12" s="5" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="M12" s="5" t="s">
         <v>20</v>
@@ -2883,10 +2928,10 @@
         <v>20</v>
       </c>
       <c r="O12" s="2" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="P12" s="2" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
     </row>
     <row r="13" s="2" customFormat="1" customHeight="1" spans="3:16">
@@ -2897,7 +2942,7 @@
         <v>501</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="F13" s="2">
         <v>10</v>
@@ -2918,7 +2963,7 @@
         <v>1</v>
       </c>
       <c r="L13" s="5" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="M13" s="5" t="s">
         <v>20</v>
@@ -2927,10 +2972,10 @@
         <v>20</v>
       </c>
       <c r="O13" s="2" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="P13" s="2" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
     </row>
     <row r="18" s="2" customFormat="1" customHeight="1" spans="3:16">
@@ -2941,7 +2986,7 @@
         <v>502</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="F18" s="2">
         <v>1</v>
@@ -2962,19 +3007,19 @@
         <v>1</v>
       </c>
       <c r="L18" s="5" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="M18" s="5" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="N18" s="5" t="s">
         <v>30</v>
       </c>
       <c r="O18" s="2" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="P18" s="2" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
     </row>
     <row r="19" customHeight="1" spans="3:16">
@@ -2985,7 +3030,7 @@
         <v>502</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="F19" s="2">
         <v>1</v>
@@ -3006,19 +3051,19 @@
         <v>1</v>
       </c>
       <c r="L19" s="5" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="M19" s="5" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="N19" s="5" t="s">
         <v>30</v>
       </c>
       <c r="O19" s="2" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="P19" s="2" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
     </row>
     <row r="20" customHeight="1" spans="3:16">
@@ -3029,7 +3074,7 @@
         <v>502</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="F20" s="2">
         <v>1</v>
@@ -3050,19 +3095,19 @@
         <v>1</v>
       </c>
       <c r="L20" s="5" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="M20" s="5" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="N20" s="5" t="s">
         <v>30</v>
       </c>
       <c r="O20" s="2" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="P20" s="2" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/AchievementConfig.xlsx
+++ b/Excel/AchievementConfig.xlsx
@@ -1,10 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\legend2\Excel\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
-    <workbookView windowHeight="17680"/>
+    <workbookView windowHeight="17680" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="属性奖励" sheetId="1" r:id="rId1"/>
@@ -175,7 +180,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="255" uniqueCount="116">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="255" uniqueCount="117">
   <si>
     <t>#</t>
   </si>
@@ -501,7 +506,7 @@
     <t>传奇人生</t>
   </si>
   <si>
-    <t>5000,5</t>
+    <t>5000,10</t>
   </si>
   <si>
     <t>？？？</t>
@@ -513,13 +518,16 @@
     <t>百折不挠</t>
   </si>
   <si>
-    <t>500,5</t>
-  </si>
-  <si>
-    <t>死亡666次</t>
+    <t>10000,10</t>
+  </si>
+  <si>
+    <t>死亡166次</t>
   </si>
   <si>
     <t>全职大师</t>
+  </si>
+  <si>
+    <t>1000,10</t>
   </si>
   <si>
     <t>上阵3系职业的技能</t>
@@ -3007,7 +3015,7 @@
         <v>1</v>
       </c>
       <c r="L18" s="5" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="M18" s="5" t="s">
         <v>108</v>
@@ -3051,7 +3059,7 @@
         <v>1</v>
       </c>
       <c r="L19" s="5" t="s">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="M19" s="5" t="s">
         <v>112</v>
@@ -3095,10 +3103,10 @@
         <v>1</v>
       </c>
       <c r="L20" s="5" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="M20" s="5" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="N20" s="5" t="s">
         <v>30</v>
@@ -3107,7 +3115,7 @@
         <v>109</v>
       </c>
       <c r="P20" s="2" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/AchievementConfig.xlsx
+++ b/Excel/AchievementConfig.xlsx
@@ -180,7 +180,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="255" uniqueCount="117">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="261" uniqueCount="120">
   <si>
     <t>#</t>
   </si>
@@ -485,6 +485,15 @@
     <t>增加暴击</t>
   </si>
   <si>
+    <t>我要打十个</t>
+  </si>
+  <si>
+    <t>22,93</t>
+  </si>
+  <si>
+    <t>增加暴伤害</t>
+  </si>
+  <si>
     <t>你不要动</t>
   </si>
   <si>
@@ -506,7 +515,7 @@
     <t>传奇人生</t>
   </si>
   <si>
-    <t>5000,10</t>
+    <t>2000,10</t>
   </si>
   <si>
     <t>？？？</t>
@@ -709,12 +718,12 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -2393,7 +2402,7 @@
         <v>307</v>
       </c>
       <c r="H37" s="2">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="I37" s="2">
         <v>4</v>
@@ -2480,7 +2489,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C1:P20"/>
+  <dimension ref="C1:P21"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16" customHeight="1"/>
   <cols>
     <col min="1" max="3" width="9" style="2"/>
@@ -2865,7 +2874,7 @@
         <v>98</v>
       </c>
       <c r="F11" s="2">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="G11" s="2">
         <v>10002</v>
@@ -2909,7 +2918,7 @@
         <v>101</v>
       </c>
       <c r="F12" s="2">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="G12" s="2">
         <v>10002</v>
@@ -2986,89 +2995,89 @@
         <v>106</v>
       </c>
     </row>
-    <row r="18" s="2" customFormat="1" customHeight="1" spans="3:16">
-      <c r="C18" s="2">
+    <row r="14" s="2" customFormat="1" customHeight="1" spans="3:16">
+      <c r="C14" s="2">
+        <v>50009</v>
+      </c>
+      <c r="D14" s="2">
+        <v>501</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="F14" s="2">
+        <v>10</v>
+      </c>
+      <c r="G14" s="2">
+        <v>10002</v>
+      </c>
+      <c r="H14" s="2">
+        <v>0</v>
+      </c>
+      <c r="I14" s="2">
+        <v>0</v>
+      </c>
+      <c r="J14" s="2">
+        <v>0</v>
+      </c>
+      <c r="K14" s="2">
+        <v>1</v>
+      </c>
+      <c r="L14" s="5" t="s">
+        <v>108</v>
+      </c>
+      <c r="M14" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="N14" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="O14" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="P14" s="2" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="19" s="2" customFormat="1" customHeight="1" spans="3:16">
+      <c r="C19" s="2">
         <v>52001</v>
-      </c>
-      <c r="D18" s="2">
-        <v>502</v>
-      </c>
-      <c r="E18" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="F18" s="2">
-        <v>1</v>
-      </c>
-      <c r="G18" s="2">
-        <v>0</v>
-      </c>
-      <c r="H18" s="2">
-        <v>0</v>
-      </c>
-      <c r="I18" s="2">
-        <v>0</v>
-      </c>
-      <c r="J18" s="2">
-        <v>0</v>
-      </c>
-      <c r="K18" s="2">
-        <v>1</v>
-      </c>
-      <c r="L18" s="5" t="s">
-        <v>86</v>
-      </c>
-      <c r="M18" s="5" t="s">
-        <v>108</v>
-      </c>
-      <c r="N18" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="O18" s="2" t="s">
-        <v>109</v>
-      </c>
-      <c r="P18" s="2" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="19" customHeight="1" spans="3:16">
-      <c r="C19" s="2">
-        <v>52002</v>
       </c>
       <c r="D19" s="2">
         <v>502</v>
       </c>
       <c r="E19" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="F19" s="2">
+        <v>1</v>
+      </c>
+      <c r="G19" s="2">
+        <v>0</v>
+      </c>
+      <c r="H19" s="2">
+        <v>0</v>
+      </c>
+      <c r="I19" s="2">
+        <v>0</v>
+      </c>
+      <c r="J19" s="2">
+        <v>0</v>
+      </c>
+      <c r="K19" s="2">
+        <v>1</v>
+      </c>
+      <c r="L19" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="M19" s="5" t="s">
         <v>111</v>
-      </c>
-      <c r="F19" s="2">
-        <v>1</v>
-      </c>
-      <c r="G19" s="2">
-        <v>0</v>
-      </c>
-      <c r="H19" s="2">
-        <v>0</v>
-      </c>
-      <c r="I19" s="2">
-        <v>0</v>
-      </c>
-      <c r="J19" s="2">
-        <v>0</v>
-      </c>
-      <c r="K19" s="2">
-        <v>1</v>
-      </c>
-      <c r="L19" s="5" t="s">
-        <v>81</v>
-      </c>
-      <c r="M19" s="5" t="s">
-        <v>112</v>
       </c>
       <c r="N19" s="5" t="s">
         <v>30</v>
       </c>
       <c r="O19" s="2" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="P19" s="2" t="s">
         <v>113</v>
@@ -3076,7 +3085,7 @@
     </row>
     <row r="20" customHeight="1" spans="3:16">
       <c r="C20" s="2">
-        <v>52003</v>
+        <v>52002</v>
       </c>
       <c r="D20" s="2">
         <v>502</v>
@@ -3103,7 +3112,7 @@
         <v>1</v>
       </c>
       <c r="L20" s="5" t="s">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="M20" s="5" t="s">
         <v>115</v>
@@ -3112,10 +3121,54 @@
         <v>30</v>
       </c>
       <c r="O20" s="2" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="P20" s="2" t="s">
         <v>116</v>
+      </c>
+    </row>
+    <row r="21" customHeight="1" spans="3:16">
+      <c r="C21" s="2">
+        <v>52003</v>
+      </c>
+      <c r="D21" s="2">
+        <v>502</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="F21" s="2">
+        <v>1</v>
+      </c>
+      <c r="G21" s="2">
+        <v>0</v>
+      </c>
+      <c r="H21" s="2">
+        <v>0</v>
+      </c>
+      <c r="I21" s="2">
+        <v>0</v>
+      </c>
+      <c r="J21" s="2">
+        <v>0</v>
+      </c>
+      <c r="K21" s="2">
+        <v>1</v>
+      </c>
+      <c r="L21" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="M21" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="N21" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="O21" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="P21" s="2" t="s">
+        <v>119</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/AchievementConfig.xlsx
+++ b/Excel/AchievementConfig.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowHeight="17680" activeTab="1"/>
+    <workbookView windowHeight="17680"/>
   </bookViews>
   <sheets>
     <sheet name="属性奖励" sheetId="1" r:id="rId1"/>
@@ -718,12 +718,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -1755,7 +1755,7 @@
         <v>3</v>
       </c>
       <c r="H8" s="2">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="I8" s="2">
         <v>1</v>

--- a/Excel/AchievementConfig.xlsx
+++ b/Excel/AchievementConfig.xlsx
@@ -1881,7 +1881,7 @@
         <v>41</v>
       </c>
       <c r="F14" s="2">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="G14" s="2">
         <v>101</v>
@@ -1991,7 +1991,7 @@
         <v>47</v>
       </c>
       <c r="F26" s="2">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="G26" s="1">
         <v>202</v>
@@ -2030,7 +2030,7 @@
         <v>50</v>
       </c>
       <c r="F27" s="2">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="G27" s="1">
         <v>203</v>
@@ -2069,7 +2069,7 @@
         <v>53</v>
       </c>
       <c r="F28" s="2">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="G28" s="2">
         <v>204</v>
@@ -2150,7 +2150,7 @@
         <v>58</v>
       </c>
       <c r="F31" s="2">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="G31" s="2">
         <v>300</v>
@@ -2191,7 +2191,7 @@
         <v>62</v>
       </c>
       <c r="F32" s="2">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="G32" s="1">
         <v>302</v>
@@ -2232,7 +2232,7 @@
         <v>66</v>
       </c>
       <c r="F33" s="2">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="G33" s="1">
         <v>303</v>
@@ -2273,7 +2273,7 @@
         <v>69</v>
       </c>
       <c r="F34" s="2">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="G34" s="1">
         <v>304</v>
@@ -2314,7 +2314,7 @@
         <v>71</v>
       </c>
       <c r="F35" s="2">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="G35" s="1">
         <v>305</v>
@@ -2355,7 +2355,7 @@
         <v>73</v>
       </c>
       <c r="F36" s="2">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="G36" s="1">
         <v>306</v>
@@ -2396,7 +2396,7 @@
         <v>75</v>
       </c>
       <c r="F37" s="2">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="G37" s="1">
         <v>307</v>
